--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T188"/>
+  <dimension ref="A1:T192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10452,7 +10452,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>500235905</t>
+          <t>500185462</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10462,18 +10462,18 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sky Habitat</t>
+          <t>Lentor Gardens Residences</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2580000</v>
+        <v>2500000</v>
       </c>
       <c r="E125" t="n">
-        <v>2065.65</v>
+        <v>2497.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10492,20 +10492,24 @@
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>88 years (TOP 2015)</t>
+          <t>102 years (TOP 2029)</t>
         </is>
       </c>
       <c r="O125" t="inlineStr"/>
@@ -10516,19 +10520,19 @@
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-habitat-500235905</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-gardens-residences-500185462</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>New listing 3 bedder for Sale!&lt;br /&gt;&lt;br /&gt;Quiet facing&lt;br /&gt;Partial furnishing&lt;br /&gt;Mins walk to amenities&lt;br /&gt;Walkable distance to Junction 8, Bishan MRT and interchange&lt;br /&gt;Tenanted to a good family @$5,900 till March 2028&lt;br /&gt;Buyers for own use has the option to pre-terminate the lease too!&lt;br</t>
+          <t>Experience unparalleled sophistication at the prestigious Lentor Gardens Residences. This exquisite three-bedroom, three-bathroom residence offers a refined living experience, featuring elegant marble flooring and modern, high-quality finishes throughout. With a generous floor area of 1,001 sqft, th</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>500149704</t>
+          <t>500235905</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10538,18 +10542,18 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Clover By The Park</t>
+          <t>Sky Habitat</t>
         </is>
       </c>
       <c r="D126" t="n">
         <v>2580000</v>
       </c>
       <c r="E126" t="n">
-        <v>2121.71</v>
+        <v>2065.65</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -10559,7 +10563,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -10571,17 +10575,17 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>88 years (TOP 2015)</t>
         </is>
       </c>
       <c r="O126" t="inlineStr"/>
@@ -10592,19 +10596,19 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-clover-by-the-park-500149704</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-habitat-500235905</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>CHEAPEST 3 BEDDER in this development!&lt;br /&gt;&lt;br /&gt;-- 5 Reasons Why this is the perfect home --&lt;br /&gt;- 1km to prestigious Catholic High Primary&lt;br /&gt;- Across from Bishan North Shopping Mall for all your grocery needs&lt;br /&gt;- Excellent Connectivity via Major Expressways (CTE, PIE) and Close Proximity t</t>
+          <t>New listing 3 bedder for Sale!&lt;br /&gt;&lt;br /&gt;Quiet facing&lt;br /&gt;Partial furnishing&lt;br /&gt;Mins walk to amenities&lt;br /&gt;Walkable distance to Junction 8, Bishan MRT and interchange&lt;br /&gt;Tenanted to a good family @$5,900 till March 2028&lt;br /&gt;Buyers for own use has the option to pre-terminate the lease too!&lt;br</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>500229536</t>
+          <t>500149704</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10614,18 +10618,18 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Thomson Grand</t>
+          <t>Clover By The Park</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2600000</v>
+        <v>2580000</v>
       </c>
       <c r="E127" t="n">
-        <v>1917.4</v>
+        <v>2121.71</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -10647,24 +10651,20 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>88 years (TOP 2015)</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>Brighthill MRT</t>
-        </is>
-      </c>
+          <t>85 years (TOP 2012)</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="b">
         <v>0</v>
@@ -10672,19 +10672,19 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-thomson-grand-500229536</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-clover-by-the-park-500149704</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEW EXCLUSIVE  LISTING! SPACIOUS 1,356 SQFT 3BR WITH PRIVATE LIFT @ THOMSON GRAND! &lt;br /&gt;&lt;br /&gt;PRICED TO SELL ! &lt;br /&gt;&lt;br /&gt;WHY THIS UNIT STANDS OUT? &lt;br /&gt;•Huge 1,356 sqft – Spacious 3BR Layout&lt;br /&gt;•Private Lift – Privacy Right to Your Doorstep&lt;br /&gt;•Generous Living &amp; Dining Areas&lt;br /&gt;•Excellent </t>
+          <t>CHEAPEST 3 BEDDER in this development!&lt;br /&gt;&lt;br /&gt;-- 5 Reasons Why this is the perfect home --&lt;br /&gt;- 1km to prestigious Catholic High Primary&lt;br /&gt;- Across from Bishan North Shopping Mall for all your grocery needs&lt;br /&gt;- Excellent Connectivity via Major Expressways (CTE, PIE) and Close Proximity t</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>24998771</t>
+          <t>500229536</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10694,18 +10694,18 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sky Vue</t>
+          <t>Thomson Grand</t>
         </is>
       </c>
       <c r="D128" t="n">
         <v>2600000</v>
       </c>
       <c r="E128" t="n">
-        <v>2278.7</v>
+        <v>1917.4</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10727,46 +10727,44 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>90 years (TOP 2017)</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>300m to Bishan Mrt</t>
-        </is>
-      </c>
+          <t>88 years (TOP 2015)</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Brighthill MRT</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
-      <c r="R128" t="b">
-        <v>1</v>
-      </c>
+      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-vue-24998771</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-thomson-grand-500229536</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>Sky Vue&lt;br /&gt;3 Bishan Street 15 S579311&lt;br /&gt;&lt;br /&gt;Required 3 month extension &lt;br /&gt;&lt;br /&gt;Call Alex Toh at 8.5.9.5.6.3.3.3 for a viewing today&lt;br /&gt;&lt;br /&gt;️ Very Well Maintained&lt;br /&gt;️ Move in condition&lt;br /&gt;Main door face out is south&lt;br /&gt;North south facing&lt;br /&gt;Owner Stay&lt;br /&gt;️Tastefully renovate</t>
+          <t xml:space="preserve">NEW EXCLUSIVE  LISTING! SPACIOUS 1,356 SQFT 3BR WITH PRIVATE LIFT @ THOMSON GRAND! &lt;br /&gt;&lt;br /&gt;PRICED TO SELL ! &lt;br /&gt;&lt;br /&gt;WHY THIS UNIT STANDS OUT? &lt;br /&gt;•Huge 1,356 sqft – Spacious 3BR Layout&lt;br /&gt;•Private Lift – Privacy Right to Your Doorstep&lt;br /&gt;•Generous Living &amp; Dining Areas&lt;br /&gt;•Excellent </t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>500134228</t>
+          <t>24998771</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10776,18 +10774,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AMO Residence</t>
+          <t>Sky Vue</t>
         </is>
       </c>
       <c r="D129" t="n">
         <v>2600000</v>
       </c>
       <c r="E129" t="n">
-        <v>2490.42</v>
+        <v>2278.7</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -10806,47 +10804,49 @@
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Middle</t>
-        </is>
-      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>13 Aug 2026</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>99 years (TOP 2026)</t>
+          <t>90 years (TOP 2017)</t>
         </is>
       </c>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>300m to Bishan Mrt</t>
+        </is>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
-      <c r="R129" t="inlineStr"/>
+      <c r="R129" t="b">
+        <v>1</v>
+      </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-amo-residence-500134228</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-vue-24998771</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>Discover your dream home in this stunning 3-bedroom condominium available for sale now! Spanning 1044 sqft, this beautiful residence at 21, Ang Mo Kio Rise, Singapore, offers both comfort and convenience. You'll find Mayflower MRT Station just 1.4 km away, making your daily commute a breeze. Familie</t>
+          <t>Sky Vue&lt;br /&gt;3 Bishan Street 15 S579311&lt;br /&gt;&lt;br /&gt;Required 3 month extension &lt;br /&gt;&lt;br /&gt;Call Alex Toh at 8.5.9.5.6.3.3.3 for a viewing today&lt;br /&gt;&lt;br /&gt;️ Very Well Maintained&lt;br /&gt;️ Move in condition&lt;br /&gt;Main door face out is south&lt;br /&gt;North south facing&lt;br /&gt;Owner Stay&lt;br /&gt;️Tastefully renovate</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>500234246</t>
+          <t>500134228</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10856,18 +10856,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>The Gardens at Bishan</t>
+          <t>AMO Residence</t>
         </is>
       </c>
       <c r="D130" t="n">
         <v>2600000</v>
       </c>
       <c r="E130" t="n">
-        <v>2155.89</v>
+        <v>2490.42</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -10888,22 +10888,22 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Middle</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>15 Aug 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>77 years (TOP 2004)</t>
+          <t>99 years (TOP 2026)</t>
         </is>
       </c>
       <c r="O130" t="inlineStr"/>
@@ -10914,19 +10914,19 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-the-gardens-at-bishan-500234246</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-amo-residence-500134228</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>SUPER CHEAP 3 BEDDER IN GARDENS @ BISHAN!&lt;br /&gt;3 BEDROOM&lt;br /&gt;1206SQFT&lt;br /&gt;Spacious&lt;br /&gt;Good layout&lt;br /&gt;Bright and Windy&lt;br /&gt;Unblocked view&lt;br /&gt;Just next to Bright Hill MRT Station and Future Cross Island Line&lt;br /&gt;Within 1km to Ai Tong School&lt;br /&gt;Don't Miss this unit! &lt;br /&gt;Call now for immed</t>
+          <t>Discover your dream home in this stunning 3-bedroom condominium available for sale now! Spanning 1044 sqft, this beautiful residence at 21, Ang Mo Kio Rise, Singapore, offers both comfort and convenience. You'll find Mayflower MRT Station just 1.4 km away, making your daily commute a breeze. Familie</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>500234589</t>
+          <t>500234246</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>15 Aug 2026</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10994,7 +10994,7 @@
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-the-gardens-at-bishan-500234589</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-the-gardens-at-bishan-500234246</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -11006,7 +11006,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>25006562</t>
+          <t>500234589</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11016,18 +11016,18 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sky Vue</t>
+          <t>The Gardens at Bishan</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>2600000</v>
       </c>
       <c r="E132" t="n">
-        <v>2278.7</v>
+        <v>2155.89</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -11046,49 +11046,47 @@
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>90 years (TOP 2017)</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>Bishan MRT</t>
-        </is>
-      </c>
+          <t>77 years (TOP 2004)</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
-      <c r="R132" t="b">
-        <v>1</v>
-      </c>
+      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-vue-25006562</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-the-gardens-at-bishan-500234589</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>RARE 3BR UNIT FOR SALES &lt;br /&gt;3BR + 2 BATH + WC + UTILITY ROOM &lt;br /&gt;RENOVATED UNIT &lt;br /&gt;NORTH SOUTH FACING &lt;br /&gt;NO WEST SUN&lt;br /&gt;AMENITIES WITHIN 5 MINS WALK &lt;br /&gt;&lt;br /&gt;2 MRT LINES NSL &amp; CCL &lt;br /&gt;3 MINS WALK TO BISHAN MRT &lt;br /&gt;5 MINS WALK TO JUNCTION 8 &lt;br /&gt;&lt;br /&gt;PRI SCHOOL (1KM) &lt;br /&gt;KUO CH</t>
+          <t>SUPER CHEAP 3 BEDDER IN GARDENS @ BISHAN!&lt;br /&gt;3 BEDROOM&lt;br /&gt;1206SQFT&lt;br /&gt;Spacious&lt;br /&gt;Good layout&lt;br /&gt;Bright and Windy&lt;br /&gt;Unblocked view&lt;br /&gt;Just next to Bright Hill MRT Station and Future Cross Island Line&lt;br /&gt;Within 1km to Ai Tong School&lt;br /&gt;Don't Miss this unit! &lt;br /&gt;Call now for immed</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>500199438</t>
+          <t>25006562</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11098,18 +11096,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lentor Hills Residences</t>
+          <t>Sky Vue</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2629999</v>
+        <v>2600000</v>
       </c>
       <c r="E133" t="n">
-        <v>2371.5</v>
+        <v>2278.7</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11119,56 +11117,58 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>CONDO</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>13 Aug 2026</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>100 years (TOP 2027)</t>
+          <t>90 years (TOP 2017)</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Lentor MRT</t>
+          <t>Bishan MRT</t>
         </is>
       </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="b">
         <v>0</v>
       </c>
-      <c r="R133" t="inlineStr"/>
+      <c r="R133" t="b">
+        <v>1</v>
+      </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500199438</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-vue-25006562</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>Unit details:&lt;br /&gt;- 1109 sqft / 103 sqm &lt;br /&gt;- 3 bed 3 bath with bomb shelter &lt;br /&gt;- be the first occupants in your new home!&lt;br /&gt;- sheltered walk to Lentor MRT and Lentor Modern Mall&lt;br /&gt;- full condo facilities &lt;br /&gt;- 2 sky terraces &lt;br /&gt;- 400m jogging track &lt;br /&gt;- early childhood developme</t>
+          <t>RARE 3BR UNIT FOR SALES &lt;br /&gt;3BR + 2 BATH + WC + UTILITY ROOM &lt;br /&gt;RENOVATED UNIT &lt;br /&gt;NORTH SOUTH FACING &lt;br /&gt;NO WEST SUN&lt;br /&gt;AMENITIES WITHIN 5 MINS WALK &lt;br /&gt;&lt;br /&gt;2 MRT LINES NSL &amp; CCL &lt;br /&gt;3 MINS WALK TO BISHAN MRT &lt;br /&gt;5 MINS WALK TO JUNCTION 8 &lt;br /&gt;&lt;br /&gt;PRI SCHOOL (1KM) &lt;br /&gt;KUO CH</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>500187970</t>
+          <t>500199438</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11178,18 +11178,18 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sky Vue</t>
+          <t>Lentor Hills Residences</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2640000</v>
+        <v>2629999</v>
       </c>
       <c r="E134" t="n">
-        <v>2313.76</v>
+        <v>2371.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11204,53 +11204,51 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>CONDO</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>90 years (TOP 2017)</t>
+          <t>100 years (TOP 2027)</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Bishan MRT</t>
+          <t>Lentor MRT</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
-      <c r="R134" t="b">
-        <v>0</v>
-      </c>
+      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-vue-500187970</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500199438</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>SUPER VALUE FOR MONEY!! NOT TO BE MISSED!!!&lt;br /&gt;Fresh on the Market!! Brand New Listing!!&lt;br /&gt;Rare Find! Spacious &amp; Bright 3-Bedroom Unit Just Steps from Bishan MRT!!&lt;br /&gt;&lt;br /&gt;Photos have undergone virtual staging.&lt;br /&gt;=========&lt;br /&gt;Sky Vue&lt;br /&gt;=========&lt;br /&gt;- Central Bishan, District 20!!&lt;b</t>
+          <t>Unit details:&lt;br /&gt;- 1109 sqft / 103 sqm &lt;br /&gt;- 3 bed 3 bath with bomb shelter &lt;br /&gt;- be the first occupants in your new home!&lt;br /&gt;- sheltered walk to Lentor MRT and Lentor Modern Mall&lt;br /&gt;- full condo facilities &lt;br /&gt;- 2 sky terraces &lt;br /&gt;- 400m jogging track &lt;br /&gt;- early childhood developme</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>500199562</t>
+          <t>500187970</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11260,18 +11258,18 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Thomson Impressions</t>
+          <t>Sky Vue</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2650000</v>
+        <v>2640000</v>
       </c>
       <c r="E135" t="n">
-        <v>2511.85</v>
+        <v>2313.76</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11281,7 +11279,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -11290,57 +11288,49 @@
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>92 years (TOP 2019)</t>
+          <t>90 years (TOP 2017)</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Bright Hill MRT</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>500m to Bright Hill MRT</t>
-        </is>
-      </c>
+          <t>Bishan MRT</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
       <c r="R135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-thomson-impressions-500199562</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-sky-vue-500187970</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>Thomson Impressions | 3 Bedroom | 1km to Ai Tong | Walk to Bright Hill MRT&lt;br /&gt;&lt;br /&gt;A Rare Family Home in One of Thomson’s Most Desirable Developments&lt;br /&gt;&lt;br /&gt;If you’re looking for a home that combines top school priority, excellent connectivity and a peaceful living environment, this is one yo</t>
+          <t>SUPER VALUE FOR MONEY!! NOT TO BE MISSED!!!&lt;br /&gt;Fresh on the Market!! Brand New Listing!!&lt;br /&gt;Rare Find! Spacious &amp; Bright 3-Bedroom Unit Just Steps from Bishan MRT!!&lt;br /&gt;&lt;br /&gt;Photos have undergone virtual staging.&lt;br /&gt;=========&lt;br /&gt;Sky Vue&lt;br /&gt;=========&lt;br /&gt;- Central Bishan, District 20!!&lt;b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>500139725</t>
+          <t>500199562</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11350,18 +11340,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lentor Hills Residences</t>
+          <t>Thomson Impressions</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2668000</v>
+        <v>2650000</v>
       </c>
       <c r="E136" t="n">
-        <v>2405.77</v>
+        <v>2511.85</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11371,18 +11361,18 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>CONDO</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -11392,35 +11382,45 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>100 years (TOP 2027)</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
+          <t>92 years (TOP 2019)</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Bright Hill MRT</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>500m to Bright Hill MRT</t>
+        </is>
+      </c>
       <c r="Q136" t="b">
         <v>0</v>
       </c>
-      <c r="R136" t="inlineStr"/>
+      <c r="R136" t="b">
+        <v>1</v>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500139725</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-thomson-impressions-500199562</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>@Not kidding | Not fishing for buyers@&lt;br /&gt;&lt;br /&gt;100% Genuine subsale, motivated seller&lt;br /&gt;External facing, mid-low floor unit&lt;br /&gt;Awesome 8888 Postal code&lt;br /&gt;Exercise of OTP to be 11 Aug 2026 onwards&lt;br /&gt;Covered walkway to Lentor MRT&lt;br /&gt;&lt;br /&gt;Within 1km&lt;br /&gt;- CHIJ St Nic&lt;br /&gt;- Anderson P</t>
+          <t>Thomson Impressions | 3 Bedroom | 1km to Ai Tong | Walk to Bright Hill MRT&lt;br /&gt;&lt;br /&gt;A Rare Family Home in One of Thomson’s Most Desirable Developments&lt;br /&gt;&lt;br /&gt;If you’re looking for a home that combines top school priority, excellent connectivity and a peaceful living environment, this is one yo</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>500154798</t>
+          <t>500139725</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11430,23 +11430,23 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lentor Gardens Residences</t>
+          <t>Lentor Hills Residences</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2684300</v>
+        <v>2668000</v>
       </c>
       <c r="E137" t="n">
-        <v>2267.15</v>
+        <v>2405.77</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -11456,31 +11456,31 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>CONDO</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Middle</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>102 years (TOP 2029)</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>Lentor MRT</t>
-        </is>
-      </c>
+          <t>100 years (TOP 2027)</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="b">
         <v>0</v>
@@ -11488,19 +11488,19 @@
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-gardens-residences-500154798</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500139725</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>***** UNBELIEVABLE PRICES!!! *****&lt;br /&gt;&lt;br /&gt;Visit the sales gallery today to see the best value you can get at Lentor Gardens Residences!&lt;br /&gt;&lt;br /&gt;Kingsford top bid at $920 PSF PPR vs $1,278 PSF PPR for next GLS site!&lt;br /&gt;+ Amongst the lowest land cost in Lentor enclave&lt;br /&gt;+ Strong demand tra</t>
+          <t>@Not kidding | Not fishing for buyers@&lt;br /&gt;&lt;br /&gt;100% Genuine subsale, motivated seller&lt;br /&gt;External facing, mid-low floor unit&lt;br /&gt;Awesome 8888 Postal code&lt;br /&gt;Exercise of OTP to be 11 Aug 2026 onwards&lt;br /&gt;Covered walkway to Lentor MRT&lt;br /&gt;&lt;br /&gt;Within 1km&lt;br /&gt;- CHIJ St Nic&lt;br /&gt;- Anderson P</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>500220857</t>
+          <t>500154798</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11510,23 +11510,23 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lentor Hills Residences</t>
+          <t>Lentor Gardens Residences</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2688000</v>
+        <v>2684300</v>
       </c>
       <c r="E138" t="n">
-        <v>2423.81</v>
+        <v>2267.15</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -11536,31 +11536,31 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>CONDO</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Middle</t>
-        </is>
-      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>100 years (TOP 2027)</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr"/>
+          <t>102 years (TOP 2029)</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Lentor MRT</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="b">
         <v>0</v>
@@ -11568,19 +11568,19 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500220857</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-gardens-residences-500154798</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Be the first to move into this brand new residence, TOP soon!&lt;br /&gt;- Located at Lentor Hills Road in District 26, this property represents a high-growth investment opportunity with immediate access to the Lentor MRT station.&lt;br /&gt;- Spanning 1,109 sqft, the efficient floor plan maximizes space and </t>
+          <t>***** UNBELIEVABLE PRICES!!! *****&lt;br /&gt;&lt;br /&gt;Visit the sales gallery today to see the best value you can get at Lentor Gardens Residences!&lt;br /&gt;&lt;br /&gt;Kingsford top bid at $920 PSF PPR vs $1,278 PSF PPR for next GLS site!&lt;br /&gt;+ Amongst the lowest land cost in Lentor enclave&lt;br /&gt;+ Strong demand tra</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>500230241</t>
+          <t>500220857</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11590,18 +11590,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Former Thomson View Condominium</t>
+          <t>Lentor Hills Residences</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>2688000</v>
       </c>
       <c r="E139" t="n">
-        <v>2685.31</v>
+        <v>2423.81</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11611,16 +11611,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>CONDO</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Middle</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>19 Aug 2026</t>
@@ -11628,12 +11632,12 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>103 years (TOP 2030)</t>
+          <t>100 years (TOP 2027)</t>
         </is>
       </c>
       <c r="O139" t="inlineStr"/>
@@ -11644,19 +11648,19 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-former-thomson-view-condominium-500230241</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500220857</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>Former Thomson View was enbloc and now redeveloped into the new Thomson Reserve.  This mega-project is in a prime location with direct sheltered link to Upper Thomson MRT &amp; doorsteps to great amenities. &lt;br /&gt;&lt;br /&gt;+ Location, connectivity, amenities &lt;br /&gt;+ Spacious &amp; efficient layout &lt;br /&gt;+ Unblo</t>
+          <t xml:space="preserve">- Be the first to move into this brand new residence, TOP soon!&lt;br /&gt;- Located at Lentor Hills Road in District 26, this property represents a high-growth investment opportunity with immediate access to the Lentor MRT station.&lt;br /&gt;- Spanning 1,109 sqft, the efficient floor plan maximizes space and </t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>500081529</t>
+          <t>500230241</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11666,18 +11670,18 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>JadeScape</t>
+          <t>Former Thomson View Condominium</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2700000</v>
+        <v>2688000</v>
       </c>
       <c r="E140" t="n">
-        <v>2667.98</v>
+        <v>2685.31</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11699,24 +11703,20 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>18 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>96 years (TOP 2023)</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>Marymount MRT</t>
-        </is>
-      </c>
+          <t>103 years (TOP 2030)</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="b">
         <v>0</v>
@@ -11724,19 +11724,19 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-jadescape-500081529</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-former-thomson-view-condominium-500230241</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>Discover this well-renovated and meticulously maintained 3-bedroom unit, perfect for a family seeking comfort, convenience, and connectivity.&lt;br /&gt;&lt;br /&gt;ꝎꝎ Jadescape ꝎꝎ&lt;br /&gt;ꝎꝎ Well Maintained Renovated 3 Bedroom ꝎꝎ&lt;br /&gt;&lt;br /&gt;&lt;br /&gt;ꝎꝎ UNIT DETAILS ꝎꝎ&lt;br /&gt;░░░░░ Almost Sold! Last Offer $2.64M  ░░░░░</t>
+          <t>Former Thomson View was enbloc and now redeveloped into the new Thomson Reserve.  This mega-project is in a prime location with direct sheltered link to Upper Thomson MRT &amp; doorsteps to great amenities. &lt;br /&gt;&lt;br /&gt;+ Location, connectivity, amenities &lt;br /&gt;+ Spacious &amp; efficient layout &lt;br /&gt;+ Unblo</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>500094471</t>
+          <t>500081529</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11746,18 +11746,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Thomson Three</t>
+          <t>JadeScape</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>2700000</v>
       </c>
       <c r="E141" t="n">
-        <v>2366.35</v>
+        <v>2667.98</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -11779,22 +11779,22 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>18 Aug 2026</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>90 years (TOP 2017)</t>
+          <t>96 years (TOP 2023)</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Upper Thomson MRT</t>
+          <t>Marymount MRT</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -11804,19 +11804,19 @@
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-thomson-three-500094471</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-jadescape-500081529</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>Within 1km to Ai Tong, 5 mins to Upper Thomson MRT&lt;br /&gt;*Serious seller, Extension to be discussed* &lt;br /&gt;&lt;br /&gt;Exclusive unit.&lt;br /&gt;&lt;br /&gt;*Description:*&lt;br /&gt;* 3 Bedroom, 3 Bathroom with Utility Room, 1,141 sqft&lt;br /&gt;* Living room Width: 3.5m &lt;br /&gt;* Height: 2.86m &lt;br /&gt;* Unblocked pool view&lt;br /&gt;*</t>
+          <t>Discover this well-renovated and meticulously maintained 3-bedroom unit, perfect for a family seeking comfort, convenience, and connectivity.&lt;br /&gt;&lt;br /&gt;ꝎꝎ Jadescape ꝎꝎ&lt;br /&gt;ꝎꝎ Well Maintained Renovated 3 Bedroom ꝎꝎ&lt;br /&gt;&lt;br /&gt;&lt;br /&gt;ꝎꝎ UNIT DETAILS ꝎꝎ&lt;br /&gt;░░░░░ Almost Sold! Last Offer $2.64M  ░░░░░</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>500130084</t>
+          <t>500094471</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11826,18 +11826,18 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Lentor Hills Residences</t>
+          <t>Thomson Three</t>
         </is>
       </c>
       <c r="D142" t="n">
         <v>2700000</v>
       </c>
       <c r="E142" t="n">
-        <v>2459.02</v>
+        <v>2366.35</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -11847,32 +11847,36 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>CONDO</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>100 years (TOP 2027)</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr"/>
+          <t>90 years (TOP 2017)</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Upper Thomson MRT</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="b">
         <v>0</v>
@@ -11880,40 +11884,40 @@
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500130084</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-thomson-three-500094471</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>Discover your dream home in this exquisite 3 bedroom, 2 bathroom apartment for sale, available now! Spanning 1098 sqft, this exceptional property is located on Lentor Hills Road (Parcel A), Ang Mo Kio, Singapore. Just a short walk from the Lentor MRT station (0.5 km), commuting is a breeze. Families</t>
+          <t>Within 1km to Ai Tong, 5 mins to Upper Thomson MRT&lt;br /&gt;*Serious seller, Extension to be discussed* &lt;br /&gt;&lt;br /&gt;Exclusive unit.&lt;br /&gt;&lt;br /&gt;*Description:*&lt;br /&gt;* 3 Bedroom, 3 Bathroom with Utility Room, 1,141 sqft&lt;br /&gt;* Living room Width: 3.5m &lt;br /&gt;* Height: 2.86m &lt;br /&gt;* Unblocked pool view&lt;br /&gt;*</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>500019893</t>
+          <t>500130084</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>hdb</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>140 Bishan Street 12</t>
+          <t>Lentor Hills Residences</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>700000</v>
+        <v>2700000</v>
       </c>
       <c r="E143" t="n">
-        <v>625.5599999999999</v>
+        <v>2459.02</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -11928,14 +11932,10 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>APT</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
@@ -11944,12 +11944,12 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>61 years (TOP 1988)</t>
+          <t>100 years (TOP 2027)</t>
         </is>
       </c>
       <c r="O143" t="inlineStr"/>
@@ -11960,19 +11960,19 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-140-bishan-street-12-500019893?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyNjQxNzg2LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTE3MTA5NiwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzMwMTEzMjAsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MiwiaWkiOiI1NWM3NzZmOTBiN2Q0YzUwOThmYjEyNjg2NjA0MDdjNyIsImRtIjozLCJmYyI6MTEwOTE3NTk3MSwiZmwiOjg2MzgzODAwOCwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTMiLCJudyI6MTExMzUsInBjIjoxMjAwMDAsIm9wIjoxMjAwMDAsIm1wIjoxMjAwMDAsImVjIjoxMjAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMGE5YWM4YmUwYWI1YTVmMTEiLCJzcCI6NzYyNzAxLCJzdCI6MTE5ODcxOCwidWsiOiIwNjAyMGZhMi1mZDBlLTRiODUtODFmYy1iOTk1YjYxNGJkOWIiLCJ0cyI6MTc4NzIyNzM0NTA1NywiYmYiOnRydWUsInBuIjoiMi0zLTQtNSIsImdjIjp0cnVlLCJnQyI6dHJ1ZSwiZ3MiOiJub25lIiwidHoiOiJVVEMiLCJldCI6MjA1fQ%26s%3D776E-fELVc_EZC63thUkV97s5tw</t>
+          <t>https://www.propertyguru.com.sg/listing/for-sale-lentor-hills-residences-500130084</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligible for ALL Races&lt;br /&gt;⭑ UNIT:&lt;br /&gt;Spacious and regular layout &lt;br /&gt;Bright and breezy&lt;br /&gt;Efficient layout, no space wastage&lt;br /&gt;&lt;br /&gt;⭑ TRANSPORT:&lt;br /&gt;Bishan MRT&lt;br /&gt;Easy connectivity to other MRTs (North East Line, Circle Line)&lt;br /&gt;         &lt;br /&gt;⭑ GROCERIES, SHOPS &amp; EATERIES&lt;br /&gt;Toa </t>
+          <t>Discover your dream home in this exquisite 3 bedroom, 2 bathroom apartment for sale, available now! Spanning 1098 sqft, this exceptional property is located on Lentor Hills Road (Parcel A), Ang Mo Kio, Singapore. Just a short walk from the Lentor MRT station (0.5 km), commuting is a breeze. Families</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>500109921</t>
+          <t>500019893</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11982,54 +11982,54 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dual Key Jumbo Unit in AMK</t>
+          <t>140 Bishan Street 12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>890000</v>
+        <v>700000</v>
       </c>
       <c r="E144" t="n">
-        <v>607.92</v>
+        <v>625.5599999999999</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>6J</t>
+          <t>4A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>18 Aug 2026</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr"/>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>L99</t>
+          <t>61 years (TOP 1988)</t>
         </is>
       </c>
       <c r="O144" t="inlineStr"/>
@@ -12040,20 +12040,19 @@
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-dual-key-jumbo-unit-in-amk-500109921?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2Ijo2MTA3MjY5LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTEwMTc3OSwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzMwMTc4NzQsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MCwiaWkiOiJjNjM2NmI3Mzk2NWI0MjQ5YmI4NWRlYjE5ZTE3ZGNkMiIsImRtIjozLCJmYyI6MTEwOTE4MjUwMSwiZmwiOjg2MzgzODcxNCwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtNC1wcm9wLWgsaGRiLTEiLCJudyI6MTExMzUsInBjIjoxMzAwMDAsIm9wIjoxMzAwMDAsIm1wIjoxMzAwMDAsImVjIjoxMzAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMGE5YWM4YmUwYWI1YTVmMTEiLCJzcCI6NzYyNzAxLCJzdCI6MTE5ODcxOCwidWsiOiIwNjAyMGZhMi1mZDBlLTRiODUtODFmYy1iOTk1YjYxNGJkOWIiLCJ0cyI6MTc4NzIyNzM0NTA1NywiYmYiOnRydWUsInBuIjoiMi0zLTQtNSIsImdjIjp0cnVlLCJnQyI6dHJ1ZSwiZ3MiOiJub25lIiwidHoiOiJVVEMiLCJldCI6MjA1fQ%26s%3DPORSWrguN3b3g5PMTBSSv0FGVXU</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-140-bishan-street-12-500019893?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyNjQxNzg2LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTE3MTA5NiwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzMwMTEzMjAsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MiwiaWkiOiI1NWM3NzZmOTBiN2Q0YzUwOThmYjEyNjg2NjA0MDdjNyIsImRtIjozLCJmYyI6MTEwOTE3NTk3MSwiZmwiOjg2MzgzODAwOCwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTMiLCJudyI6MTExMzUsInBjIjoxMjAwMDAsIm9wIjoxMjAwMDAsIm1wIjoxMjAwMDAsImVjIjoxMjAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMGE5YWM4YmUwYWI1YTVmMTEiLCJzcCI6NzYyNzAxLCJzdCI6MTE5ODcxOCwidWsiOiIwNjAyMGZhMi1mZDBlLTRiODUtODFmYy1iOTk1YjYxNGJkOWIiLCJ0cyI6MTc4NzIyNzM0NTA1NywiYmYiOnRydWUsInBuIjoiMi0zLTQtNSIsImdjIjp0cnVlLCJnQyI6dHJ1ZSwiZ3MiOiJub25lIiwidHoiOiJVVEMiLCJldCI6MjA1fQ%26s%3D776E-fELVc_EZC63thUkV97s5tw</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>5-RM Adjoined HDB at 182 Ang Mo Kio Avenue 5&lt;br /&gt;&lt;br /&gt;1464 sqft / 136 sqm&lt;br /&gt;High Floor&lt;br /&gt;Generous space, can be configured for multiple use&lt;br /&gt;Perfect for multi-gen living or part-stay part rental living&lt;br /&gt;Dual Entrances for Dual key concept -&lt;br /&gt;Potential to craft 6 Bedrooms, plus hel</t>
+          <t xml:space="preserve">Eligible for ALL Races&lt;br /&gt;⭑ UNIT:&lt;br /&gt;Spacious and regular layout &lt;br /&gt;Bright and breezy&lt;br /&gt;Efficient layout, no space wastage&lt;br /&gt;&lt;br /&gt;⭑ TRANSPORT:&lt;br /&gt;Bishan MRT&lt;br /&gt;Easy connectivity to other MRTs (North East Line, Circle Line)&lt;br /&gt;         &lt;br /&gt;⭑ GROCERIES, SHOPS &amp; EATERIES&lt;br /&gt;Toa </t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>500201525</t>
+          <t>500236979</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12063,18 +12062,18 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>112B Alkaff Crescent</t>
+          <t>264 Bishan Street 24</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>980000</v>
+        <v>800000</v>
       </c>
       <c r="E145" t="n">
-        <v>979.02</v>
+        <v>701.14</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12094,12 +12093,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Ground</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -12109,39 +12108,37 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>94 years (TOP 2021)</t>
+          <t>64 years (TOP 1991)</t>
         </is>
       </c>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>500m to Woodleigh MRT</t>
-        </is>
-      </c>
+      <c r="P145" t="inlineStr"/>
       <c r="Q145" t="b">
         <v>1</v>
       </c>
-      <c r="R145" t="inlineStr"/>
+      <c r="R145" t="b">
+        <v>0</v>
+      </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-112b-alkaff-crescent-500201525?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyMzI3ODY1LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ2Mzc0MSwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzI0OTE2NzIsImRpIjoiNDJjNWZhNDFiNzEzNDUzNjg5MjQ1YjE3MWJkMTFjYzQiLCJkaiI6NCwiaWkiOiIxMWQwNzhlMzlhNDU0ZTcyOTFlMzcxOWM5NThmYTkzYSIsImRtIjozLCJmYyI6MTEwODY1NDk1NiwiZmwiOjg2MzgzMjk4MywiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTI1IiwibnciOjExMTM1LCJwYyI6MTEwMDAwLCJvcCI6MTEwMDAwLCJtcCI6MTEwMDAwLCJlYyI6MTEwMDAwLCJnbSI6MCwiZXAiOm51bGwsInByIjoyMzU3MTQsInJ0IjoyLCJycyI6NTAwLCJzYSI6IjgxIiwic2IiOiJpLTBjODdjMjc0YmE2OTQxNDIyIiwic3AiOjc2MzMxMCwic3QiOjExOTg3MTgsInVrIjoiMDYwMjBmYTItZmQwZS00Yjg1LTgxZmMtYjk5NWI2MTRiZDliIiwidHMiOjE3ODcyMjczNDg1ODAsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3DppK3jWcMkBbKounGfkrnGfPq41E</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-264-bishan-street-24-500236979?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjozMzAwNzY5LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ2MzA0NiwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzIzMjgyNjUsImRpIjoiMWJlMmQ3NmY0Y2QyNGI4YzlhNDhlOGM4NmU5ZjU0ZGEiLCJkaiI6NCwiaWkiOiJjNTg1N2QxZGUzZWY0ZjE2YjhhOTMyNjRhMWEwZjRkYSIsImRtIjozLCJmYyI6MTEwODQ4OTc0NywiZmwiOjg2MzgzMTUxOSwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTMiLCJudyI6MTExMzUsInBjIjoxMTAwMDAsIm9wIjoxMTAwMDAsIm1wIjoxMTAwMDAsImVjIjoxMTAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMDdiZWY5Mzk3MzZmOTYxOWQiLCJzcCI6MTI2NDQ3Mywic3QiOjExOTg3MTgsInVrIjoiYzlhYmIwNmUtM2YyMC00NmIyLTliNTctZmVhYjZjZDRlMTliIiwidHMiOjE3ODcyODA4MDkzNDMsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3D3HG3I8fV-7fd2-IU4fcO6SbvX6I</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>Bright, windy and high-floor corner home in the heart of Bidadari&lt;br /&gt;&lt;br /&gt;- High-floor unit with open, unblocked views&lt;br /&gt;- Overlooking the Cedar campus and landed homes&lt;br /&gt;- Less than 500m to Woodleigh MRT and Mall&lt;br /&gt;&lt;br /&gt;*EIP Quota: Currently eligible for Malay and Indian/Other buyers o</t>
+          <t>Discover the perfect sanctuary for your family in this beautifully renovated corner unit located at 264 Bishan Street 24.&lt;br /&gt;&lt;br /&gt;This 1141 sqft home offers the ideal balance of space, comfort, and convenience, making it a standout choice for those looking to settle in one of Singapore most sough</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>500224774</t>
+          <t>500109921</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12151,38 +12148,38 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>156 Lorong 1 Toa Payoh</t>
+          <t>Dual Key Jumbo Unit in AMK</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1000000</v>
+        <v>890000</v>
       </c>
       <c r="E146" t="n">
-        <v>919.12</v>
+        <v>607.92</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>6J</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12192,17 +12189,13 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>5 Aug 2026</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
+          <t>18 Aug 2026</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>72 years (TOP 1999)</t>
+          <t>L99</t>
         </is>
       </c>
       <c r="O146" t="inlineStr"/>
@@ -12210,24 +12203,23 @@
       <c r="Q146" t="b">
         <v>0</v>
       </c>
-      <c r="R146" t="b">
-        <v>0</v>
-      </c>
+      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-156-lorong-1-toa-payoh-500224774?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyMzAwNjU0LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ0MTU3NiwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzEzMzUyOTQsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6NCwiaWkiOiIzODVlNTdhOGRhMzc0MzZjODY0ZjNkMTJlZWFjMWZkNCIsImRtIjozLCJmYyI6MTEwNzQ5MjgwNywiZmwiOjg2MzgyMDg1NiwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTI1IiwibnciOjExMTM1LCJwYyI6MTEwMDAwLCJvcCI6MTEwMDAwLCJtcCI6MTEwMDAwLCJlYyI6MTEwMDAwLCJnbSI6MCwiZXAiOm51bGwsInByIjoyMzU3MTQsInJ0IjoyLCJycyI6NTAwLCJzYSI6IjgxIiwic2IiOiJpLTBhOWFjOGJlMGFiNWE1ZjExIiwic3AiOjc2MjcwMSwic3QiOjExOTg3MTgsInVrIjoiMDYwMjBmYTItZmQwZS00Yjg1LTgxZmMtYjk5NWI2MTRiZDliIiwidHMiOjE3ODcyMjczNDUwNTgsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3D5WxXcGkQBF4SdnHp5rETjBUWqLE</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-dual-key-jumbo-unit-in-amk-500109921?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2Ijo2MTA3MjY5LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTEwMTc3OSwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzMwMTc4NzQsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MCwiaWkiOiJjNjM2NmI3Mzk2NWI0MjQ5YmI4NWRlYjE5ZTE3ZGNkMiIsImRtIjozLCJmYyI6MTEwOTE4MjUwMSwiZmwiOjg2MzgzODcxNCwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtNC1wcm9wLWgsaGRiLTEiLCJudyI6MTExMzUsInBjIjoxMzAwMDAsIm9wIjoxMzAwMDAsIm1wIjoxMzAwMDAsImVjIjoxMzAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMGE5YWM4YmUwYWI1YTVmMTEiLCJzcCI6NzYyNzAxLCJzdCI6MTE5ODcxOCwidWsiOiIwNjAyMGZhMi1mZDBlLTRiODUtODFmYy1iOTk1YjYxNGJkOWIiLCJ0cyI6MTc4NzIyNzM0NTA1NywiYmYiOnRydWUsInBuIjoiMi0zLTQtNSIsImdjIjp0cnVlLCJnQyI6dHJ1ZSwiZ3MiOiJub25lIiwidHoiOiJVVEMiLCJldCI6MjA1fQ%26s%3DPORSWrguN3b3g5PMTBSSv0FGVXU</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>New exclusive listing &lt;br /&gt;&lt;br /&gt;Nicely and tastefully renovated. Pure selling. No extension requested. &lt;br /&gt;&lt;br /&gt;Excellent Connectivity&lt;br /&gt;• Fully Sheltered Walkway to Toa Payoh MRT Station &amp; HDB Hub&lt;br /&gt;• Near Toa Payoh Bus Interchange&lt;br /&gt;&lt;br /&gt;Superb Amenities nearby&lt;br /&gt;• HDB Hub&lt;br /&gt;•</t>
+          <t>5-RM Adjoined HDB at 182 Ang Mo Kio Avenue 5&lt;br /&gt;&lt;br /&gt;1464 sqft / 136 sqm&lt;br /&gt;High Floor&lt;br /&gt;Generous space, can be configured for multiple use&lt;br /&gt;Perfect for multi-gen living or part-stay part rental living&lt;br /&gt;Dual Entrances for Dual key concept +&lt;br /&gt;Potential to craft 6 Bedrooms, plus hel</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>60024586</t>
+          <t>500234057</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12237,23 +12229,23 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>152 Lorong 2 Toa Payoh</t>
+          <t>110A Bidadari Park Drive</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1100000</v>
+        <v>948888</v>
       </c>
       <c r="E147" t="n">
-        <v>929.05</v>
+        <v>947.9400000000001</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -12263,7 +12255,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>4A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -12271,45 +12263,53 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>29 Jul 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>78 years (TOP 2005)</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr"/>
+          <t>94 years (TOP 2021)</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Woodleigh MRT</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R147" t="b">
         <v>1</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-152-lorong-2-toa-payoh-60024586</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-110a-bidadari-park-drive-500234057?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyNzYyNTI0LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ1NjM3MSwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzE1MTg2MjIsImRpIjoiN2I3NDBiMWVlYTdlNDZkYWIwZjZlYmIxMzI4NDRkYWMiLCJkaiI6NCwiaWkiOiJlYzBlODdhMTc0ZDc0NzY4YTY2ODlhNGJhZmU3YjUyNyIsImRtIjozLCJmYyI6MTEwNzY3NjEzNiwiZmwiOjg2MzgyMjM4OSwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtNC1wcm9wLWgsaGRiLTI1IiwibnciOjExMTM1LCJwYyI6MTEwMDAwLCJvcCI6MTEwMDAwLCJtcCI6MTEwMDAwLCJlYyI6MTEwMDAwLCJnbSI6MCwiZXAiOm51bGwsInByIjoyMzU3MTQsInJ0IjoyLCJycyI6NTAwLCJzYSI6IjgxIiwic2IiOiJpLTBiZDI5MGY3ZTg1OWE4YjFmIiwic3AiOjEyNTg0NjksInN0IjoxMTk4NzE4LCJ1ayI6ImM5YWJiMDZlLTNmMjAtNDZiMi05YjU3LWZlYWI2Y2Q0ZTE5YiIsInRzIjoxNzg3MjgwNzkyMzk0LCJiZiI6dHJ1ZSwicG4iOiIyLTMtNC01IiwiZ2MiOnRydWUsImdDIjp0cnVlLCJncyI6Im5vbmUiLCJ0eiI6IlVUQyIsImV0IjoyMDV9%26s%3DkxKItwKZB7FFIdgbyOWxHHMRzZU</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>152 Lorong 2 Toa Payoh – Spacious 5-Room Flat (Improved) For Sale&lt;br /&gt;&lt;br /&gt;Property Details:&lt;br /&gt;	•	Flat Type: 5-Room Improved (5I)&lt;br /&gt;	•	Size: 110 sqm / 1,184 sqft&lt;br /&gt;	•	Extension Required: 3 months&lt;br /&gt;	•	Ethnic Quota: Chinese quota filled (as of July 2026)&lt;br /&gt;	•	Built Year: January 2006</t>
+          <t>!!! S.U.P.E.R C.H.E.A.P !!! Starting from ONLY $948,888&lt;br /&gt;&lt;br /&gt;MOP 7 Sep 2026&lt;br /&gt;&lt;br /&gt;Unit Details:&lt;br /&gt;* Renovations Savings! Just Move in!&lt;br /&gt;* Bright and airy&lt;br /&gt;* #01 floor&lt;br /&gt;* 5 mins walk to Woodleigh Mall&lt;br /&gt;* 5 mins walk to Woodleigh MRT&lt;br /&gt;* Main door: NW&lt;br /&gt;* Living roo</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>500238585</t>
+          <t>500201525</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12319,14 +12319,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>591A Ang Mo Kio Street 51</t>
+          <t>112B Alkaff Crescent</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1128000</v>
+        <v>980000</v>
       </c>
       <c r="E148" t="n">
-        <v>1126.87</v>
+        <v>979.02</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12345,51 +12345,59 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>4NG</t>
+          <t>4A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>18 Aug 2026</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>90 years (TOP 2017)</t>
+          <t>94 years (TOP 2021)</t>
         </is>
       </c>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>500m to Woodleigh MRT</t>
+        </is>
+      </c>
       <c r="Q148" t="b">
         <v>1</v>
       </c>
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-591a-ang-mo-kio-street-51-500238585?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyODE4OTA0LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ2NDcyMywiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzI3MjczNTMsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MSwiaWkiOiJjNDgyM2E3ZjIwOTg0OTAwODk5N2JkNjgzYzk2ZDk1ZiIsImRtIjozLCJmYyI6MTEwODg5MTcyNiwiZmwiOjg2MzgzNTIwOCwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTEiLCJudyI6MTExMzUsInBjIjoxMjAwMDAsIm9wIjoxMjAwMDAsIm1wIjoxMjAwMDAsImVjIjoxMjAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMGE5YWM4YmUwYWI1YTVmMTEiLCJzcCI6NzYyNzAxLCJzdCI6MTE5ODcxOCwidWsiOiIwNjAyMGZhMi1mZDBlLTRiODUtODFmYy1iOTk1YjYxNGJkOWIiLCJ0cyI6MTc4NzIyNzM0NTA1NywiYmYiOnRydWUsInBuIjoiMi0zLTQtNSIsImdjIjp0cnVlLCJnQyI6dHJ1ZSwiZ3MiOiJub25lIiwidHoiOiJVVEMiLCJldCI6MjA1fQ%26s%3DX04HH4n6sGWjOxBoRI4yEXx0yyA</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-112b-alkaff-crescent-500201525?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyMzI3ODY1LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ2Mzc0MSwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzI0OTE2NzIsImRpIjoiNDJjNWZhNDFiNzEzNDUzNjg5MjQ1YjE3MWJkMTFjYzQiLCJkaiI6NCwiaWkiOiIxMWQwNzhlMzlhNDU0ZTcyOTFlMzcxOWM5NThmYTkzYSIsImRtIjozLCJmYyI6MTEwODY1NDk1NiwiZmwiOjg2MzgzMjk4MywiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTI1IiwibnciOjExMTM1LCJwYyI6MTEwMDAwLCJvcCI6MTEwMDAwLCJtcCI6MTEwMDAwLCJlYyI6MTEwMDAwLCJnbSI6MCwiZXAiOm51bGwsInByIjoyMzU3MTQsInJ0IjoyLCJycyI6NTAwLCJzYSI6IjgxIiwic2IiOiJpLTBjODdjMjc0YmE2OTQxNDIyIiwic3AiOjc2MzMxMCwic3QiOjExOTg3MTgsInVrIjoiMDYwMjBmYTItZmQwZS00Yjg1LTgxZmMtYjk5NWI2MTRiZDliIiwidHMiOjE3ODcyMjczNDg1ODAsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3DppK3jWcMkBbKounGfkrnGfPq41E</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>Nicely Renovated, Unblock City View, Spacious&lt;br /&gt;&lt;br /&gt;Key feature&lt;br /&gt;✓ Move-in condition &lt;br /&gt;✓ Well-maintained and renovated condition &lt;br /&gt;✓ Spacious and Functional layout &lt;br /&gt;✓ Bright and airy - NS direction&lt;br /&gt;✓ Corner unit&lt;br /&gt;✓ Unblocked city view - can see fireworks&lt;br /&gt;✓ Open co</t>
+          <t>Bright, windy and high-floor corner home in the heart of Bidadari&lt;br /&gt;&lt;br /&gt;- High-floor unit with open, unblocked views&lt;br /&gt;- Overlooking the Cedar campus and landed homes&lt;br /&gt;- Less than 500m to Woodleigh MRT and Mall&lt;br /&gt;&lt;br /&gt;*EIP Quota: Currently eligible for Malay and Indian/Other buyers o</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>500043629</t>
+          <t>500222327</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12399,18 +12407,18 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>138A Lorong 1A Toa Payoh</t>
+          <t>123 Bishan Street 12</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1150000</v>
+        <v>988000</v>
       </c>
       <c r="E149" t="n">
-        <v>945.72</v>
+        <v>882.14</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -12425,15 +12433,19 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>4A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>19 Aug 2026</t>
@@ -12441,39 +12453,35 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>58 years (TOP 1985)</t>
         </is>
       </c>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>1.1 km away and Toa Payoh MRT</t>
-        </is>
-      </c>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500043629</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-123-bishan-street-12-500222327?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2Ijo2Mjc5NzE4LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ1NDQzNCwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzI3NjA3OTYsImRpIjoiY2FjNDlhYmFkMWQ2NDdkNWI3OGJmNTQzYmMyZDJjOTYiLCJkaiI6NCwiaWkiOiIxYzZhZTJkOGU0Zjc0N2M4OTIwMWUxY2NjZjA5NGY2NyIsImRtIjozLCJmYyI6MTEwODkyNTE2OSwiZmwiOjg2MzgzNjI2NSwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTMiLCJudyI6MTExMzUsInBjIjoxMTAwMDAsIm9wIjoxMTAwMDAsIm1wIjoxMTAwMDAsImVjIjoxMTAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMGM4N2MyNzRiYTY5NDE0MjIiLCJzcCI6MTI1MTEwMSwic3QiOjExOTg3MTgsInVrIjoiYzlhYmIwNmUtM2YyMC00NmIyLTliNTctZmVhYjZjZDRlMTliIiwidHMiOjE3ODcyODA3ODg1ODcsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3DSuMKwfMhA_-oVgIxxvc9CG_28p0</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>138A Lorong 1A Toa Payoh for Sale!&lt;br /&gt;&lt;br /&gt;- 5I&lt;br /&gt;- 3 Beds, 2 Baths&lt;br /&gt;- Spacious layout&lt;br /&gt;- Nicely renovated&lt;br /&gt;- Bright and windy&lt;br /&gt;- Near MRT&lt;br /&gt;- Near amenities&lt;br /&gt;- Superb location&lt;br /&gt;- Serious sellers&lt;br /&gt;&lt;br /&gt;Please contact 90.90.76.81 Aina for an Exclusive viewing!&lt;br</t>
+          <t>123 Bishan Street 12 | District 20 | 1119 SQFT | Award Winning Designer Home&lt;br /&gt;&lt;br /&gt;Unit Details:&lt;br /&gt;&lt;br /&gt;* 100% Move-in Condition Unit&lt;br /&gt;* Thoughtfully Designed Living Space &lt;br /&gt;* Custom-built carpentry with extensive storage solutions&lt;br /&gt;* Premium materials and designer fittings&lt;br /</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>500229691</t>
+          <t>500224774</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12483,18 +12491,18 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>138B Lorong 1A Toa Payoh</t>
+          <t>156 Lorong 1 Toa Payoh</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1150000</v>
+        <v>1000000</v>
       </c>
       <c r="E150" t="n">
-        <v>945.72</v>
+        <v>919.12</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -12509,7 +12517,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>4A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -12517,20 +12525,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>5 Aug 2026</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>72 years (TOP 1999)</t>
         </is>
       </c>
       <c r="O150" t="inlineStr"/>
@@ -12538,22 +12550,24 @@
       <c r="Q150" t="b">
         <v>0</v>
       </c>
-      <c r="R150" t="inlineStr"/>
+      <c r="R150" t="b">
+        <v>0</v>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138b-lorong-1a-toa-payoh-500229691</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-156-lorong-1-toa-payoh-500224774?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyMzAwNjU0LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ0MTU3NiwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzEzMzUyOTQsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6NCwiaWkiOiIzODVlNTdhOGRhMzc0MzZjODY0ZjNkMTJlZWFjMWZkNCIsImRtIjozLCJmYyI6MTEwNzQ5MjgwNywiZmwiOjg2MzgyMDg1NiwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTI1IiwibnciOjExMTM1LCJwYyI6MTEwMDAwLCJvcCI6MTEwMDAwLCJtcCI6MTEwMDAwLCJlYyI6MTEwMDAwLCJnbSI6MCwiZXAiOm51bGwsInByIjoyMzU3MTQsInJ0IjoyLCJycyI6NTAwLCJzYSI6IjgxIiwic2IiOiJpLTBhOWFjOGJlMGFiNWE1ZjExIiwic3AiOjc2MjcwMSwic3QiOjExOTg3MTgsInVrIjoiMDYwMjBmYTItZmQwZS00Yjg1LTgxZmMtYjk5NWI2MTRiZDliIiwidHMiOjE3ODcyMjczNDUwNTgsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3D5WxXcGkQBF4SdnHp5rETjBUWqLE</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>Unit Highlights&lt;br /&gt;Size: 1,216 sqft&lt;br /&gt;Main door facing: Northeast &lt;br /&gt;Balcony facing: Northwest &lt;br /&gt;Remaining lease: 84 years 9 months (as of Aug 2026)&lt;br /&gt;Ethnic quota restrictions apply. Please enquire to check eligibility&lt;br /&gt;&lt;br /&gt;Getting Around&lt;br /&gt;Braddell MRT — 450m&lt;br /&gt;Toa Payoh</t>
+          <t>New exclusive listing &lt;br /&gt;&lt;br /&gt;Nicely and tastefully renovated. Pure selling. No extension requested. &lt;br /&gt;&lt;br /&gt;Excellent Connectivity&lt;br /&gt;• Fully Sheltered Walkway to Toa Payoh MRT Station &amp; HDB Hub&lt;br /&gt;• Near Toa Payoh Bus Interchange&lt;br /&gt;&lt;br /&gt;Superb Amenities nearby&lt;br /&gt;• HDB Hub&lt;br /&gt;•</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>500200632</t>
+          <t>60024586</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12563,14 +12577,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>138C Lorong 1A Toa Payoh</t>
+          <t>152 Lorong 2 Toa Payoh</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1170000</v>
+        <v>1100000</v>
       </c>
       <c r="E151" t="n">
-        <v>988.1799999999999</v>
+        <v>929.05</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12589,7 +12603,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>5A</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -12597,53 +12611,45 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>29 Jul 2026</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>78 years (TOP 2005)</t>
         </is>
       </c>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>500m to TPY MRT or Braddell MRT</t>
-        </is>
-      </c>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500200632</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-152-lorong-2-toa-payoh-60024586</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;- for low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- huge balcony and living room!&lt;br /&gt;- spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- super accessib</t>
+          <t>152 Lorong 2 Toa Payoh – Spacious 5-Room Flat (Improved) For Sale&lt;br /&gt;&lt;br /&gt;Property Details:&lt;br /&gt;	•	Flat Type: 5-Room Improved (5I)&lt;br /&gt;	•	Size: 110 sqm / 1,184 sqft&lt;br /&gt;	•	Extension Required: 3 months&lt;br /&gt;	•	Ethnic Quota: Chinese quota filled (as of July 2026)&lt;br /&gt;	•	Built Year: January 2006</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>500203234</t>
+          <t>500238585</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12653,18 +12659,18 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>138C Lorong 1A Toa Payoh</t>
+          <t>591A Ang Mo Kio Street 51</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1170000</v>
+        <v>1128000</v>
       </c>
       <c r="E152" t="n">
-        <v>988.1799999999999</v>
+        <v>1126.87</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -12679,61 +12685,51 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>5A</t>
+          <t>4NG</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>90 years (TOP 2017)</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>500m to TPY MRT or Braddell MRT</t>
-        </is>
-      </c>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="b">
-        <v>0</v>
-      </c>
-      <c r="R152" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500203234</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-591a-ang-mo-kio-street-51-500238585?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyODE4OTA0LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTQ2NDcyMywiY2giOjU5NTM0LCJjayI6e30sImNyIjo5MzI3MjczNTMsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MSwiaWkiOiJjNDgyM2E3ZjIwOTg0OTAwODk5N2JkNjgzYzk2ZDk1ZiIsImRtIjozLCJmYyI6MTEwODg5MTcyNiwiZmwiOjg2MzgzNTIwOCwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTEiLCJudyI6MTExMzUsInBjIjoxMjAwMDAsIm9wIjoxMjAwMDAsIm1wIjoxMjAwMDAsImVjIjoxMjAwMDAsImdtIjowLCJlcCI6bnVsbCwicHIiOjIzNTcxNCwicnQiOjIsInJzIjo1MDAsInNhIjoiODEiLCJzYiI6ImktMGE5YWM4YmUwYWI1YTVmMTEiLCJzcCI6NzYyNzAxLCJzdCI6MTE5ODcxOCwidWsiOiIwNjAyMGZhMi1mZDBlLTRiODUtODFmYy1iOTk1YjYxNGJkOWIiLCJ0cyI6MTc4NzIyNzM0NTA1NywiYmYiOnRydWUsInBuIjoiMi0zLTQtNSIsImdjIjp0cnVlLCJnQyI6dHJ1ZSwiZ3MiOiJub25lIiwidHoiOiJVVEMiLCJldCI6MjA1fQ%26s%3DX04HH4n6sGWjOxBoRI4yEXx0yyA</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t xml:space="preserve">138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;-  Low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- Huge balcony and living room!&lt;br /&gt;- Spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- Super accessible </t>
+          <t>Nicely Renovated, Unblock City View, Spacious&lt;br /&gt;&lt;br /&gt;Key feature&lt;br /&gt;✓ Move-in condition &lt;br /&gt;✓ Well-maintained and renovated condition &lt;br /&gt;✓ Spacious and Functional layout &lt;br /&gt;✓ Bright and airy - NS direction&lt;br /&gt;✓ Corner unit&lt;br /&gt;✓ Unblocked city view - can see fireworks&lt;br /&gt;✓ Open co</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>500106085</t>
+          <t>500043629</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12743,18 +12739,18 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>138C Lorong 1A Toa Payoh</t>
+          <t>138A Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1170000</v>
+        <v>1150000</v>
       </c>
       <c r="E153" t="n">
-        <v>988.1799999999999</v>
+        <v>945.72</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -12769,7 +12765,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -12777,14 +12773,10 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12800,30 +12792,28 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>500m to TPY MRT or Braddell MRT</t>
+          <t>1.1 km away and Toa Payoh MRT</t>
         </is>
       </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
-      <c r="R153" t="b">
-        <v>0</v>
-      </c>
+      <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500106085</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500043629</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;- for low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- huge balcony and living room!&lt;br /&gt;- spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- super accessib</t>
+          <t>138A Lorong 1A Toa Payoh for Sale!&lt;br /&gt;&lt;br /&gt;- 5I&lt;br /&gt;- 3 Beds, 2 Baths&lt;br /&gt;- Spacious layout&lt;br /&gt;- Nicely renovated&lt;br /&gt;- Bright and windy&lt;br /&gt;- Near MRT&lt;br /&gt;- Near amenities&lt;br /&gt;- Superb location&lt;br /&gt;- Serious sellers&lt;br /&gt;&lt;br /&gt;Please contact 90.90.76.81 Aina for an Exclusive viewing!&lt;br</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>500188787</t>
+          <t>500229691</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12833,18 +12823,18 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>138C Lorong 1A Toa Payoh</t>
+          <t>138B Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1170000</v>
+        <v>1150000</v>
       </c>
       <c r="E154" t="n">
-        <v>988.1799999999999</v>
+        <v>945.72</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -12867,14 +12857,10 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12888,30 +12874,26 @@
         </is>
       </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>500m to both Toa Payoh MRT and Braddell MRT</t>
-        </is>
-      </c>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500188787</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138b-lorong-1a-toa-payoh-500229691</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>Contact Valerie Kang 923.489.63 for exclusive viewing today!&lt;br /&gt;&lt;br /&gt;Key highlights:&lt;br /&gt;- Well-renovated and move-in ready&lt;br /&gt;- Spacious and efficient squarish layout (no wasted space or odd shape)&lt;br /&gt;- All bedrooms fit queen/king-size bed + study area comfortably&lt;br /&gt;- Bright and airy liv</t>
+          <t>Unit Highlights&lt;br /&gt;Size: 1,216 sqft&lt;br /&gt;Main door facing: Northeast &lt;br /&gt;Balcony facing: Northwest &lt;br /&gt;Remaining lease: 84 years 9 months (as of Aug 2026)&lt;br /&gt;Ethnic quota restrictions apply. Please enquire to check eligibility&lt;br /&gt;&lt;br /&gt;Getting Around&lt;br /&gt;Braddell MRT — 450m&lt;br /&gt;Toa Payoh</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>500188798</t>
+          <t>500200632</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12947,7 +12929,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -12955,10 +12937,14 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>3 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12974,28 +12960,30 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>500m to both Toa Payoh MRT and Braddell MRT</t>
+          <t>500m to TPY MRT or Braddell MRT</t>
         </is>
       </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
-      <c r="R155" t="inlineStr"/>
+      <c r="R155" t="b">
+        <v>0</v>
+      </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500188798</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500200632</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>Contact 9088.1098 for exclusive viewing today!&lt;br /&gt;&lt;br /&gt;Key highlights:&lt;br /&gt;- Well-renovated and move-in ready&lt;br /&gt;- Spacious and efficient squarish layout (no wasted space or odd shape)&lt;br /&gt;- All bedrooms fit queen/king-size bed + study area comfortably&lt;br /&gt;- Bright and airy living &amp; dining a</t>
+          <t>138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;- for low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- huge balcony and living room!&lt;br /&gt;- spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- super accessib</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>500199767</t>
+          <t>500203234</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13046,7 +13034,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -13073,19 +13061,19 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500199767</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500203234</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;- for low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- huge balcony and living room!&lt;br /&gt;- spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- super accessib</t>
+          <t xml:space="preserve">138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;-  Low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- Huge balcony and living room!&lt;br /&gt;- Spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- Super accessible </t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>500200561</t>
+          <t>500106085</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13121,7 +13109,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>5A</t>
+          <t>5PA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13136,7 +13124,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -13163,7 +13151,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500200561</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500106085</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
@@ -13175,7 +13163,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>500204463</t>
+          <t>500188787</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13185,18 +13173,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>588D Ang Mo Kio Street 52</t>
+          <t>138C Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1180000</v>
+        <v>1170000</v>
       </c>
       <c r="E158" t="n">
-        <v>979.25</v>
+        <v>988.1799999999999</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -13211,55 +13199,59 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5PA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>15 Aug 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>84 years (TOP 2011)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>500m to both Toa Payoh MRT and Braddell MRT</t>
+        </is>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500204463</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500188787</t>
         </is>
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>√ High floor &lt;br /&gt;√ No West Sun. &lt;br /&gt;√ Not Facing Expressway. &lt;br /&gt;√ 1st Owner. &lt;br /&gt;√ Opposite Cheng San Market&lt;br /&gt;&lt;br /&gt;√ This active listing is ideal for those looking for a long-term residence providing stability and potential for future appreciation.&lt;br /&gt;&lt;br /&gt;√ Built in 2011, this well</t>
+          <t>Contact Valerie Kang 923.489.63 for exclusive viewing today!&lt;br /&gt;&lt;br /&gt;Key highlights:&lt;br /&gt;- Well-renovated and move-in ready&lt;br /&gt;- Spacious and efficient squarish layout (no wasted space or odd shape)&lt;br /&gt;- All bedrooms fit queen/king-size bed + study area comfortably&lt;br /&gt;- Bright and airy liv</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>500125049</t>
+          <t>500188798</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13269,18 +13261,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>588D Ang Mo Kio Street 52</t>
+          <t>138C Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1180000</v>
+        <v>1170000</v>
       </c>
       <c r="E159" t="n">
-        <v>979.25</v>
+        <v>988.1799999999999</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -13295,55 +13287,55 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5PA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>4 Aug 2026</t>
+          <t>3 Aug 2026</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>84 years (TOP 2011)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>500m to both Toa Payoh MRT and Braddell MRT</t>
+        </is>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500125049</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500188798</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discover an exceptional opportunity to own a spacious HDB DBSS at 588D Ang Mo Kio Street 52, located in District 20. Built in 2011, this well-maintained unit offers a practical layout with 3 bedrooms, 2 bathrooms and 2 balcony(Living &amp; Master) perfect for first-time buyers, young professionals, and </t>
+          <t>Contact 9088.1098 for exclusive viewing today!&lt;br /&gt;&lt;br /&gt;Key highlights:&lt;br /&gt;- Well-renovated and move-in ready&lt;br /&gt;- Spacious and efficient squarish layout (no wasted space or odd shape)&lt;br /&gt;- All bedrooms fit queen/king-size bed + study area comfortably&lt;br /&gt;- Bright and airy living &amp; dining a</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>500189946</t>
+          <t>500199767</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13353,18 +13345,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>588D Ang Mo Kio Street 52</t>
+          <t>138C Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1180000</v>
+        <v>1170000</v>
       </c>
       <c r="E160" t="n">
-        <v>979.25</v>
+        <v>988.1799999999999</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -13379,55 +13371,61 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>13 Aug 2026</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>84 years (TOP 2011)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>500m to TPY MRT or Braddell MRT</t>
+        </is>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
-      <c r="R160" t="inlineStr"/>
+      <c r="R160" t="b">
+        <v>0</v>
+      </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500189946</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500199767</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>Discover an exceptional opportunity to own a spacious HDB apartment at 588D Ang Mo Kio Street 52, located in District 20. Built in 2011, this well-maintained unit offers a practical layout with 3 bedrooms, 2 bathrooms and 2 balcony(Living &amp; Master) perfect for first-time buyers, young professionals,</t>
+          <t>138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;- for low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- huge balcony and living room!&lt;br /&gt;- spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- super accessib</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>500233216</t>
+          <t>500200561</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13437,18 +13435,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>588D Ang Mo Kio Street 52</t>
+          <t>138C Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1180000</v>
+        <v>1170000</v>
       </c>
       <c r="E161" t="n">
-        <v>979.25</v>
+        <v>988.1799999999999</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -13463,55 +13461,61 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>2 Aug 2026</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>84 years (TOP 2011)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>500m to TPY MRT or Braddell MRT</t>
+        </is>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
-      <c r="R161" t="inlineStr"/>
+      <c r="R161" t="b">
+        <v>0</v>
+      </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500233216</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500200561</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>Discover an exceptional opportunity to own a spacious HDB apartment at 588D Ang Mo Kio Street 52, located in District 20. Built in 2011, this well-maintained unit offers a practical layout with 3 bedrooms, 2 bathrooms and 2 balcony(Living &amp; Master) perfect for first-time buyers, young professionals,</t>
+          <t>138C Lor 1A Toa Payoh&lt;br /&gt;- 5rm DBSS&lt;br /&gt;- 110sqm/1184sqft&lt;br /&gt;- for low floor lovers!&lt;br /&gt;- Well renovated and maintained!&lt;br /&gt;- 2 balconies &lt;br /&gt;- huge balcony and living room!&lt;br /&gt;- spacious bedrooms that can fit queen size beds!&lt;br /&gt;- 500m to TPY MRT or Braddell MRT&lt;br /&gt;- super accessib</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>500161793</t>
+          <t>500204463</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13521,18 +13525,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>261 Toa Payoh Apex</t>
+          <t>588D Ang Mo Kio Street 52</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1200000</v>
+        <v>1180000</v>
       </c>
       <c r="E162" t="n">
-        <v>1198.8</v>
+        <v>979.25</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -13547,12 +13551,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -13562,40 +13566,40 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>15 Aug 2026</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>91 years (TOP 2018)</t>
+          <t>84 years (TOP 2011)</t>
         </is>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-261-toa-payoh-apex-500161793?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyNzc5MDE0LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTIyODIzNCwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5Mjk2NDQyMjQsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MywiaWkiOiIwZGU0MjBhZDViY2I0NzQ3YmUzZTE1OTRmZTUwYWZhNyIsImRtIjozLCJmYyI6MTEwNTc5NjA4NSwiZmwiOjg2Mzc4MzU5MSwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTI1IiwibnciOjExMTM1LCJwYyI6MTIwMDAwLCJvcCI6MTIwMDAwLCJtcCI6MTIwMDAwLCJlYyI6MTIwMDAwLCJnbSI6MCwiZXAiOm51bGwsInByIjoyMzU3MTQsInJ0IjoyLCJycyI6NTAwLCJzYSI6IjgxIiwic2IiOiJpLTBhOWFjOGJlMGFiNWE1ZjExIiwic3AiOjc2MjcwMSwic3QiOjExOTg3MTgsInVrIjoiMDYwMjBmYTItZmQwZS00Yjg1LTgxZmMtYjk5NWI2MTRiZDliIiwidHMiOjE3ODcyMjczNDUwNTgsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3DW8gsxgUj-a_kWSVCeNaxxPezagw</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500204463</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>[Why This Home Stands Out]&lt;br /&gt;&lt;br /&gt;Rare high-floor 4-room HDB offers the winning combination many buyers look for — privacy, brightness, breeze, unblocked views, no west sun, and daily convenience right at your doorstep.&lt;br /&gt;&lt;br /&gt;Located in one of Singapore’s most established mature estates, th</t>
+          <t>√ High floor &lt;br /&gt;√ No West Sun. &lt;br /&gt;√ Not Facing Expressway. &lt;br /&gt;√ 1st Owner. &lt;br /&gt;√ Opposite Cheng San Market&lt;br /&gt;&lt;br /&gt;√ This active listing is ideal for those looking for a long-term residence providing stability and potential for future appreciation.&lt;br /&gt;&lt;br /&gt;√ Built in 2011, this well</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>500230372</t>
+          <t>500125049</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13605,18 +13609,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>596A Ang Mo Kio Street 52</t>
+          <t>588D Ang Mo Kio Street 52</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1200000</v>
+        <v>1180000</v>
       </c>
       <c r="E163" t="n">
-        <v>1013.51</v>
+        <v>979.25</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -13631,7 +13635,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>5A</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -13646,17 +13650,17 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>4 Aug 2026</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>73 years (TOP 2000)</t>
+          <t>84 years (TOP 2011)</t>
         </is>
       </c>
       <c r="O163" t="inlineStr"/>
@@ -13664,24 +13668,22 @@
       <c r="Q163" t="b">
         <v>0</v>
       </c>
-      <c r="R163" t="b">
-        <v>0</v>
-      </c>
+      <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-596a-ang-mo-kio-street-52-500230372</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500125049</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discover this exceptional 5A HDB unit located at 596A Ang Mo Kio Street 52. Positioned on a high floor, this residence offers a generous floor area of 1,184 sqft, providing a comfortable and well-ventilated living environment. The layout features three spacious bedrooms and two bathrooms, making it </t>
+          <t xml:space="preserve">Discover an exceptional opportunity to own a spacious HDB DBSS at 588D Ang Mo Kio Street 52, located in District 20. Built in 2011, this well-maintained unit offers a practical layout with 3 bedrooms, 2 bathrooms and 2 balcony(Living &amp; Master) perfect for first-time buyers, young professionals, and </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>60066059</t>
+          <t>500189946</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13691,18 +13693,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>260B Kebun Baru Court</t>
+          <t>588D Ang Mo Kio Street 52</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1216000</v>
+        <v>1180000</v>
       </c>
       <c r="E164" t="n">
-        <v>1000</v>
+        <v>979.25</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -13727,22 +13729,22 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>91 years (TOP 2018)</t>
+          <t>84 years (TOP 2011)</t>
         </is>
       </c>
       <c r="O164" t="inlineStr"/>
@@ -13750,24 +13752,22 @@
       <c r="Q164" t="b">
         <v>0</v>
       </c>
-      <c r="R164" t="b">
-        <v>1</v>
-      </c>
+      <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-260b-kebun-baru-court-60066059</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500189946</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>Open to any buyer, regardless of their ethnic group and citizenship.&lt;br /&gt;Requires 3 months extension stay after HDB completion.&lt;br /&gt;&lt;br /&gt;113 sqm/ 1216 sqf, 5 Room HDB Flat, First owners, Chinese.&lt;br /&gt;Renovated.&lt;br /&gt;Spacious layout, squarish with no odd corners or slanting walls.&lt;br /&gt;&lt;br /&gt;Walk</t>
+          <t>Discover an exceptional opportunity to own a spacious HDB apartment at 588D Ang Mo Kio Street 52, located in District 20. Built in 2011, this well-maintained unit offers a practical layout with 3 bedrooms, 2 bathrooms and 2 balcony(Living &amp; Master) perfect for first-time buyers, young professionals,</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>25558333</t>
+          <t>500233216</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13777,18 +13777,18 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>138A Lorong 1A Toa Payoh</t>
+          <t>588D Ang Mo Kio Street 52</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1250000</v>
+        <v>1180000</v>
       </c>
       <c r="E165" t="n">
-        <v>1027.96</v>
+        <v>979.25</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -13803,55 +13803,55 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>84 years (TOP 2011)</t>
         </is>
       </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-25558333</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-588d-ang-mo-kio-street-52-500233216</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>HDB DBSS 5RM FOR SALE&lt;br /&gt;&lt;br /&gt;- Unit is Renovated and well kept!&lt;br /&gt;- Premium Stack for Sale&lt;br /&gt;- Corner Unit&lt;br /&gt;- Balcony in the hall and master room&lt;br /&gt;- Renovated&lt;br /&gt;- Good size in the hall and dinning area&lt;br /&gt;- Huge Master Room&lt;br /&gt;- Excellent and Fantastic location&lt;br /&gt;- Well K</t>
+          <t>Discover an exceptional opportunity to own a spacious HDB apartment at 588D Ang Mo Kio Street 52, located in District 20. Built in 2011, this well-maintained unit offers a practical layout with 3 bedrooms, 2 bathrooms and 2 balcony(Living &amp; Master) perfect for first-time buyers, young professionals,</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>500194415</t>
+          <t>500161793</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13861,18 +13861,18 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>138C Lorong 1A Toa Payoh</t>
+          <t>261 Toa Payoh Apex</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1250000</v>
+        <v>1200000</v>
       </c>
       <c r="E166" t="n">
-        <v>1055.74</v>
+        <v>1198.8</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>4A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -13907,39 +13907,35 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>91 years (TOP 2018)</t>
         </is>
       </c>
       <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>500 m to Toa Payoh and Bradelll MRT</t>
-        </is>
-      </c>
+      <c r="P166" t="inlineStr"/>
       <c r="Q166" t="b">
         <v>1</v>
       </c>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500194415</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-261-toa-payoh-apex-500161793?pixelUrl=https%3A%2F%2Fe-11135.adzerk.net%2Fe.gif%3Fe%3DeyJ2IjoiMS4xNCIsImF2IjoyNzc5MDE0LCJhdCI6MTYzLCJidCI6MCwiY20iOjY1OTIyODIzNCwiY2giOjU5NTM0LCJjayI6e30sImNyIjo5Mjk2NDQyMjQsImRpIjoiMGQ2MDRmODMxOGYwNGJiNzg3OTk4ZTUzZmZmZWM0MDciLCJkaiI6MywiaWkiOiIwZGU0MjBhZDViY2I0NzQ3YmUzZTE1OTRmZTUwYWZhNyIsImRtIjozLCJmYyI6MTEwNTc5NjA4NSwiZmwiOjg2Mzc4MzU5MSwiaXAiOiIxMTIuMTk5LjIyMS4xNzAiLCJrdyI6Imxpc3Rpbmctc2FsZS1iZWRzLTMtcHJvcC1oLGxpc3Rpbmctc2FsZS1iZWRzLTQtcHJvcC1oLGhkYi0xLGhkYi0yNSxoZGItMyIsIm1rIjoibGlzdGluZy1zYWxlLWJlZHMtMy1wcm9wLWgsaGRiLTI1IiwibnciOjExMTM1LCJwYyI6MTIwMDAwLCJvcCI6MTIwMDAwLCJtcCI6MTIwMDAwLCJlYyI6MTIwMDAwLCJnbSI6MCwiZXAiOm51bGwsInByIjoyMzU3MTQsInJ0IjoyLCJycyI6NTAwLCJzYSI6IjgxIiwic2IiOiJpLTBhOWFjOGJlMGFiNWE1ZjExIiwic3AiOjc2MjcwMSwic3QiOjExOTg3MTgsInVrIjoiMDYwMjBmYTItZmQwZS00Yjg1LTgxZmMtYjk5NWI2MTRiZDliIiwidHMiOjE3ODcyMjczNDUwNTgsImJmIjp0cnVlLCJwbiI6IjItMy00LTUiLCJnYyI6dHJ1ZSwiZ0MiOnRydWUsImdzIjoibm9uZSIsInR6IjoiVVRDIiwiZXQiOjIwNX0%26s%3DW8gsxgUj-a_kWSVCeNaxxPezagw</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>Good location in a much  sought after and mature Housing Estate.&lt;br /&gt;July etnic quota - Chinese cant buy. Only minority races.&lt;br /&gt;Corner unit 5 Room&lt;br /&gt;Spacious layout&lt;br /&gt;Bedrooms can take in a queen/king size bedsets.&lt;br /&gt;Fully air conditioned. &lt;br /&gt;Large balcony that can  double  up as an</t>
+          <t>[Why This Home Stands Out]&lt;br /&gt;&lt;br /&gt;Rare high-floor 4-room HDB offers the winning combination many buyers look for — privacy, brightness, breeze, unblocked views, no west sun, and daily convenience right at your doorstep.&lt;br /&gt;&lt;br /&gt;Located in one of Singapore’s most established mature estates, th</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>500216052</t>
+          <t>500230372</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13949,18 +13945,18 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>310B Ang Mo Kio Avenue 1</t>
+          <t>596A Ang Mo Kio Street 52</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1250000</v>
+        <v>1200000</v>
       </c>
       <c r="E167" t="n">
-        <v>960.0599999999999</v>
+        <v>1013.51</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -13975,7 +13971,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -13983,45 +13979,49 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>84 years (TOP 2011)</t>
+          <t>73 years (TOP 2000)</t>
         </is>
       </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-310b-ang-mo-kio-avenue-1-500216052</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-596a-ang-mo-kio-street-52-500230372</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t xml:space="preserve">[NEW EXCLUSIVE LISTING]&lt;br /&gt;&lt;br /&gt;► Property Type : HDB 5 Room Improved, corner unit&lt;br /&gt;► Size : 121 sqm / 1,302 sqft&lt;br /&gt;► Completed 2011, approximately 14 years old&lt;br /&gt;► Lease Start Date: 2012, Balance lease approximately 85 years 3 months&lt;br /&gt;&lt;br /&gt;Park facing corner stacks are limited in </t>
+          <t xml:space="preserve">Discover this exceptional 5A HDB unit located at 596A Ang Mo Kio Street 52. Positioned on a high floor, this residence offers a generous floor area of 1,184 sqft, providing a comfortable and well-ventilated living environment. The layout features three spacious bedrooms and two bathrooms, making it </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>500204552</t>
+          <t>60066059</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14031,18 +14031,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>143 Lorong 2 Toa Payoh</t>
+          <t>260B Kebun Baru Court</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1260000</v>
+        <v>1216000</v>
       </c>
       <c r="E168" t="n">
-        <v>1064.19</v>
+        <v>1000</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -14062,50 +14062,52 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Middle</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>7 Aug 2026</t>
+          <t>13 Aug 2026</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>75 years (TOP 2002)</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>Toa Payoh MRT</t>
-        </is>
-      </c>
+          <t>91 years (TOP 2018)</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
-      <c r="R168" t="inlineStr"/>
+      <c r="R168" t="b">
+        <v>1</v>
+      </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-143-lorong-2-toa-payoh-500204552</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-260b-kebun-baru-court-60066059</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>***RARELY AVAILABLE 5RM FOR SALE***&lt;br /&gt;***EXCELLENT LOCATION***&lt;br /&gt;&lt;br /&gt;This image has been generated or enhanced using AI for illustration purposes only&lt;br /&gt;&lt;br /&gt;5rm 1184sqft &lt;br /&gt;Lease start 2002 &lt;br /&gt;&lt;br /&gt;SPACIOUS 5rm&lt;br /&gt;- 3 bedroom &amp; 2 bath &lt;br /&gt;&lt;br /&gt;HIGH FLOOR&lt;br /&gt;- Located above</t>
+          <t>Open to any buyer, regardless of their ethnic group and citizenship.&lt;br /&gt;Requires 3 months extension stay after HDB completion.&lt;br /&gt;&lt;br /&gt;113 sqm/ 1216 sqf, 5 Room HDB Flat, First owners, Chinese.&lt;br /&gt;Renovated.&lt;br /&gt;Spacious layout, squarish with no odd corners or slanting walls.&lt;br /&gt;&lt;br /&gt;Walk</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>500192619</t>
+          <t>25558333</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14115,18 +14117,18 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>143 Lorong 2 Toa Payoh</t>
+          <t>138A Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1260000</v>
+        <v>1250000</v>
       </c>
       <c r="E169" t="n">
-        <v>1064.19</v>
+        <v>1027.96</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -14141,7 +14143,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5PA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -14151,22 +14153,22 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>5 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>75 years (TOP 2002)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O169" t="inlineStr"/>
@@ -14177,19 +14179,19 @@
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-143-lorong-2-toa-payoh-500192619</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-25558333</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>Discover the perfect family sanctuary in this beautifully renovated high floor corner unit located in the heart of Toa Payoh. Offering an expansive 1,184 square feet of well-designed living space, this 5I HDB apartment provides the ideal canvas for your dream home. Experience unparalleled privacy an</t>
+          <t>HDB DBSS 5RM FOR SALE&lt;br /&gt;&lt;br /&gt;- Unit is Renovated and well kept!&lt;br /&gt;- Premium Stack for Sale&lt;br /&gt;- Corner Unit&lt;br /&gt;- Balcony in the hall and master room&lt;br /&gt;- Renovated&lt;br /&gt;- Good size in the hall and dinning area&lt;br /&gt;- Huge Master Room&lt;br /&gt;- Excellent and Fantastic location&lt;br /&gt;- Well K</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>500207178</t>
+          <t>500194415</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14199,18 +14201,18 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>143 Lorong 2 Toa Payoh</t>
+          <t>138C Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1260000</v>
+        <v>1250000</v>
       </c>
       <c r="E170" t="n">
-        <v>1063.29</v>
+        <v>1055.74</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -14235,47 +14237,49 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>24 Jul 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>75 years (TOP 2002)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>500 m to Toa Payoh and Bradelll MRT</t>
+        </is>
+      </c>
       <c r="Q170" t="b">
-        <v>0</v>
-      </c>
-      <c r="R170" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-143-lorong-2-toa-payoh-500207178</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-500194415</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>closing soon.&lt;br /&gt;&lt;br /&gt;super high floor 5 room unit, regular layout and 3bedrooms intact. superb location with good schools in the vicinity&lt;br /&gt;&lt;br /&gt;no agents fees required, no extension.&lt;br /&gt;suitable for transitioning families who have a tight timeline&lt;br /&gt;&lt;br /&gt;call now to view</t>
+          <t>Good location in a much  sought after and mature Housing Estate.&lt;br /&gt;July etnic quota - Chinese cant buy. Only minority races.&lt;br /&gt;Corner unit 5 Room&lt;br /&gt;Spacious layout&lt;br /&gt;Bedrooms can take in a queen/king size bedsets.&lt;br /&gt;Fully air conditioned. &lt;br /&gt;Large balcony that can  double  up as an</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>500216888</t>
+          <t>500216052</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14285,18 +14289,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>444 Sin Ming Avenue</t>
+          <t>310B Ang Mo Kio Avenue 1</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1280000</v>
+        <v>1250000</v>
       </c>
       <c r="E171" t="n">
-        <v>990.71</v>
+        <v>960.0599999999999</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -14316,50 +14320,48 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>30 Jul 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>63 years (TOP 1990)</t>
+          <t>84 years (TOP 2011)</t>
         </is>
       </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="b">
-        <v>0</v>
-      </c>
-      <c r="R171" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R171" t="b">
+        <v>1</v>
+      </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-444-sin-ming-avenue-500216888</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-310b-ang-mo-kio-avenue-1-500216052</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>When the owner renovated this flat before he moved in, he put in sitting benches and the dining table right against the window, cos the unblocked view from this unit is literally a million-dollar view. What's more, the constant breeze that flows through the flat was precious, and the natural light f</t>
+          <t xml:space="preserve">[NEW EXCLUSIVE LISTING]&lt;br /&gt;&lt;br /&gt;► Property Type : HDB 5 Room Improved, corner unit&lt;br /&gt;► Size : 121 sqm / 1,302 sqft&lt;br /&gt;► Completed 2011, approximately 14 years old&lt;br /&gt;► Lease Start Date: 2012, Balance lease approximately 85 years 3 months&lt;br /&gt;&lt;br /&gt;Park facing corner stacks are limited in </t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>500174875</t>
+          <t>500204552</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14369,14 +14371,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>138A Lorong 1A Toa Payoh</t>
+          <t>143 Lorong 2 Toa Payoh</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1288888</v>
+        <v>1260000</v>
       </c>
       <c r="E172" t="n">
-        <v>1088.59</v>
+        <v>1064.19</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14395,7 +14397,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>5S</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -14403,53 +14405,47 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Ground</t>
-        </is>
-      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>18 Aug 2026</t>
+          <t>7 Aug 2026</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>75 years (TOP 2002)</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Braddell MRT</t>
+          <t>Toa Payoh MRT</t>
         </is>
       </c>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
-      <c r="R172" t="b">
-        <v>1</v>
-      </c>
+      <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500174875</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-143-lorong-2-toa-payoh-500204552</t>
         </is>
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>3 bed 2 bath&lt;br /&gt;High ceiling&lt;br /&gt;For Ground Floor Lovers&lt;br /&gt;Bomb Shelter Included&lt;br /&gt;No West Sun&lt;br /&gt;Well maintained&lt;br /&gt;Perfect for families&lt;br /&gt;Regular Layout&lt;br /&gt;No Odd Shape&lt;br /&gt;6min walk to Braddell MRT&lt;br /&gt;7min to CHIJ Primary Toa Payoh&lt;br /&gt;Preschool Nearby&lt;br /&gt;2min walk to seve</t>
+          <t>***RARELY AVAILABLE 5RM FOR SALE***&lt;br /&gt;***EXCELLENT LOCATION***&lt;br /&gt;&lt;br /&gt;This image has been generated or enhanced using AI for illustration purposes only&lt;br /&gt;&lt;br /&gt;5rm 1184sqft &lt;br /&gt;Lease start 2002 &lt;br /&gt;&lt;br /&gt;SPACIOUS 5rm&lt;br /&gt;- 3 bedroom &amp; 2 bath &lt;br /&gt;&lt;br /&gt;HIGH FLOOR&lt;br /&gt;- Located above</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>500219660</t>
+          <t>500192619</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14459,14 +14455,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>139B Lorong 1A Toa Payoh</t>
+          <t>143 Lorong 2 Toa Payoh</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1295000</v>
+        <v>1260000</v>
       </c>
       <c r="E173" t="n">
-        <v>1093.75</v>
+        <v>1064.19</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14485,7 +14481,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>5S</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -14493,43 +14489,47 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>5 Aug 2026</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>75 years (TOP 2002)</t>
         </is>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-139b-lorong-1a-toa-payoh-500219660</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-143-lorong-2-toa-payoh-500192619</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>New Listing for Sale at 139B Toa Payoh! &lt;br /&gt;&lt;br /&gt;Experience the perfect blend of comfort and convenience in the heart of Toa Payoh. This expansive 5-room HDB unit offers a generous 1184 sqft of living space, thoughtfully designed for modern families who value both room to breathe and proximity to</t>
+          <t>Discover the perfect family sanctuary in this beautifully renovated high floor corner unit located in the heart of Toa Payoh. Offering an expansive 1,184 square feet of well-designed living space, this 5I HDB apartment provides the ideal canvas for your dream home. Experience unparalleled privacy an</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>500153545</t>
+          <t>500207178</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14539,18 +14539,18 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>138A Lorong 1A Toa Payoh</t>
+          <t>143 Lorong 2 Toa Payoh</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1300000</v>
+        <v>1260000</v>
       </c>
       <c r="E174" t="n">
-        <v>1069.08</v>
+        <v>1063.29</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -14575,22 +14575,22 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>1 Aug 2026</t>
+          <t>24 Jul 2026</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>75 years (TOP 2002)</t>
         </is>
       </c>
       <c r="O174" t="inlineStr"/>
@@ -14598,22 +14598,24 @@
       <c r="Q174" t="b">
         <v>0</v>
       </c>
-      <c r="R174" t="inlineStr"/>
+      <c r="R174" t="b">
+        <v>0</v>
+      </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500153545</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-143-lorong-2-toa-payoh-500207178</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>Looking for rare 5room DBSS unit, here is one you should not miss:&lt;br /&gt;&lt;br /&gt;* 5-room, Design Build &amp; Sell model. DBSS&lt;br /&gt;* 113 sqm, 1216 sqft, suitable for big family with kids / couple&lt;br /&gt;* Low floor, greenery facing, great privacy, quiet, peaceful&lt;br /&gt;* Well maintained, cosy, homely feeling</t>
+          <t>closing soon.&lt;br /&gt;&lt;br /&gt;super high floor 5 room unit, regular layout and 3bedrooms intact. superb location with good schools in the vicinity&lt;br /&gt;&lt;br /&gt;no agents fees required, no extension.&lt;br /&gt;suitable for transitioning families who have a tight timeline&lt;br /&gt;&lt;br /&gt;call now to view</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>500197020</t>
+          <t>500216888</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14623,18 +14625,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>145 Lorong 2 Toa Payoh</t>
+          <t>444 Sin Ming Avenue</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1328888</v>
+        <v>1280000</v>
       </c>
       <c r="E175" t="n">
-        <v>1122.37</v>
+        <v>990.71</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -14649,61 +14651,55 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>5A</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>15 Aug 2026</t>
+          <t>30 Jul 2026</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>78 years (TOP 2005)</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>Tpy MRT</t>
-        </is>
-      </c>
+          <t>63 years (TOP 1990)</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
-      <c r="R175" t="b">
-        <v>1</v>
-      </c>
+      <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-145-lorong-2-toa-payoh-500197020</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-444-sin-ming-avenue-500216888</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t xml:space="preserve">A rare n superb location 5rm&lt;br /&gt;- Centrally located near TPY mrt&lt;br /&gt;- Stone throw from All amenities food ctr  &lt;br /&gt;   supermkt &amp; shops  &lt;br /&gt;- Exclusive Point Block Design&lt;br /&gt;- Privacy Corner&lt;br /&gt;- Bright &amp; Breezy&lt;br /&gt;- Within 1km CHIJ , Mary mount Convent&lt;br /&gt;-  Chinese eligible&lt;br /&gt;- </t>
+          <t>When the owner renovated this flat before he moved in, he put in sitting benches and the dining table right against the window, cos the unblocked view from this unit is literally a million-dollar view. What's more, the constant breeze that flows through the flat was precious, and the natural light f</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>500169348</t>
+          <t>500174875</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14713,14 +14709,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>79C Toa Payoh Central</t>
+          <t>138A Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1350000</v>
+        <v>1288888</v>
       </c>
       <c r="E176" t="n">
-        <v>1140.2</v>
+        <v>1088.59</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14739,7 +14735,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5S</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -14747,7 +14743,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>18 Aug 2026</t>
@@ -14755,35 +14755,41 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>82 years (TOP 2009)</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr"/>
+          <t>85 years (TOP 2012)</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Braddell MRT</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
-      <c r="R176" t="inlineStr"/>
+      <c r="R176" t="b">
+        <v>1</v>
+      </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-79c-toa-payoh-central-500169348</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500174875</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>New Exclusive Listing&lt;br /&gt;5I HDB for Sale&lt;br /&gt;Floor Area: 1,184sqft&lt;br /&gt;&lt;br /&gt;GENERAL INFO:&lt;br /&gt;-1km to several primary schools: CHIJ (TPY) and Pei Chun&lt;br /&gt;-Right across a ton of eateries and amenities&lt;br /&gt;-Stone's throw to Toa Payoh MRT and Interchange&lt;br /&gt;-Easy access to PIE and CTE&lt;br /&gt;&lt;</t>
+          <t>3 bed 2 bath&lt;br /&gt;High ceiling&lt;br /&gt;For Ground Floor Lovers&lt;br /&gt;Bomb Shelter Included&lt;br /&gt;No West Sun&lt;br /&gt;Well maintained&lt;br /&gt;Perfect for families&lt;br /&gt;Regular Layout&lt;br /&gt;No Odd Shape&lt;br /&gt;6min walk to Braddell MRT&lt;br /&gt;7min to CHIJ Primary Toa Payoh&lt;br /&gt;Preschool Nearby&lt;br /&gt;2min walk to seve</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>500225300</t>
+          <t>500219660</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14793,18 +14799,18 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>228B Ang Mo Kio Street 23</t>
+          <t>139B Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1350000</v>
+        <v>1295000</v>
       </c>
       <c r="E177" t="n">
-        <v>1110.2</v>
+        <v>1093.75</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -14819,57 +14825,51 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5S</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>6 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>94 years (TOP 2021)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="b">
-        <v>1</v>
-      </c>
-      <c r="R177" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-228b-ang-mo-kio-street-23-500225300</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-139b-lorong-1a-toa-payoh-500219660</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>Exclusive Listing&lt;br /&gt;&lt;br /&gt;UNIT HIGHLIGHTS&lt;br /&gt;- North-South facing&lt;br /&gt;- High floor&lt;br /&gt;- Unblocked city view&lt;br /&gt;- Standalone corner unit&lt;br /&gt;- Move-in condition&lt;br /&gt;&lt;br /&gt;LOCATION &amp; AMENITIES&lt;br /&gt;- Supermarket &amp; Eateries - right across &lt;br /&gt;- Mayflower MRT - ~5mins walk&lt;br /&gt;&lt;br /&gt;*3-mo</t>
+          <t>New Listing for Sale at 139B Toa Payoh! &lt;br /&gt;&lt;br /&gt;Experience the perfect blend of comfort and convenience in the heart of Toa Payoh. This expansive 5-room HDB unit offers a generous 1184 sqft of living space, thoughtfully designed for modern families who value both room to breathe and proximity to</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>500210793</t>
+          <t>500153545</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14879,14 +14879,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>228A Ang Mo Kio Street 23</t>
+          <t>138A Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1388000</v>
+        <v>1300000</v>
       </c>
       <c r="E178" t="n">
-        <v>1141.45</v>
+        <v>1069.08</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14905,51 +14905,55 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5PA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>1 Aug 2026</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>93 years (TOP 2020)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-228a-ang-mo-kio-street-23-500210793</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500153545</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t xml:space="preserve">*GENIUNE LISTING* by Element Properties&lt;br /&gt;By Appointment only. Call to book your viewing!&lt;br /&gt;&lt;br /&gt;Lease left: Approx. 94 years&lt;br /&gt;Corner Unit, North-South Facing, Stand Alone unit, Excellent Privacy&lt;br /&gt;New Listing • Renovated • Move-in Condition • Unblocked Views &lt;br /&gt;&lt;br /&gt;Property Flat </t>
+          <t>Looking for rare 5room DBSS unit, here is one you should not miss:&lt;br /&gt;&lt;br /&gt;* 5-room, Design Build &amp; Sell model. DBSS&lt;br /&gt;* 113 sqm, 1216 sqft, suitable for big family with kids / couple&lt;br /&gt;* Low floor, greenery facing, great privacy, quiet, peaceful&lt;br /&gt;* Well maintained, cosy, homely feeling</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>25492867</t>
+          <t>500197020</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14959,18 +14963,18 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>138C Lorong 1A Toa Payoh</t>
+          <t>145 Lorong 2 Toa Payoh</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1400000</v>
+        <v>1328888</v>
       </c>
       <c r="E179" t="n">
-        <v>1111.99</v>
+        <v>1122.37</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -14995,49 +14999,51 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Middle</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>15 Aug 2026</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>78 years (TOP 2005)</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Braddell MRT</t>
+          <t>Tpy MRT</t>
         </is>
       </c>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
-      <c r="R179" t="inlineStr"/>
+      <c r="R179" t="b">
+        <v>1</v>
+      </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-25492867</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-145-lorong-2-toa-payoh-500197020</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spacious 5-Room HDB for Sale at 138C Lorong 1A Toa Payoh  &lt;br /&gt;(Not Eligible for Chinese Buyers Due to Ethnic Quota)&lt;br /&gt;&lt;br /&gt;Discover this well-maintained 5-room HDB flat located in the highly sought-after Toa Payoh area. Situated at 138C Lorong 1A Toa Payoh, this unit offers a perfect blend of </t>
+          <t xml:space="preserve">A rare n superb location 5rm&lt;br /&gt;- Centrally located near TPY mrt&lt;br /&gt;- Stone throw from All amenities food ctr  &lt;br /&gt;   supermkt &amp; shops  &lt;br /&gt;- Exclusive Point Block Design&lt;br /&gt;- Privacy Corner&lt;br /&gt;- Bright &amp; Breezy&lt;br /&gt;- Within 1km CHIJ , Mary mount Convent&lt;br /&gt;-  Chinese eligible&lt;br /&gt;- </t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>60139647</t>
+          <t>500169348</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15047,18 +15053,18 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>141 Lorong 2 Toa Payoh</t>
+          <t>79C Toa Payoh Central</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1448888</v>
+        <v>1350000</v>
       </c>
       <c r="E180" t="n">
-        <v>1160.97</v>
+        <v>1140.2</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -15073,7 +15079,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>5A</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -15084,24 +15090,20 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>18 Aug 2026</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>72 years (TOP 1999)</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>Toa Payoh MRT</t>
-        </is>
-      </c>
+          <t>82 years (TOP 2009)</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="b">
         <v>0</v>
@@ -15109,19 +15111,19 @@
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-141-lorong-2-toa-payoh-60139647</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-79c-toa-payoh-central-500169348</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>A once-in-a-lifetime chance to own the only 5-bedroom HDB unit currently available next to Toa Payoh MRT. With zero supply in the market, this is an extremely rare opportunity for families and investors.&lt;br /&gt;&lt;br /&gt;Premium High-Floor Living&lt;br /&gt;Bright and airy with floor-to-ceiling windows, offerin</t>
+          <t>New Exclusive Listing&lt;br /&gt;5I HDB for Sale&lt;br /&gt;Floor Area: 1,184sqft&lt;br /&gt;&lt;br /&gt;GENERAL INFO:&lt;br /&gt;-1km to several primary schools: CHIJ (TPY) and Pei Chun&lt;br /&gt;-Right across a ton of eateries and amenities&lt;br /&gt;-Stone's throw to Toa Payoh MRT and Interchange&lt;br /&gt;-Easy access to PIE and CTE&lt;br /&gt;&lt;</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>500192670</t>
+          <t>500225300</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15131,18 +15133,18 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>138B Lorong 1A Toa Payoh</t>
+          <t>228B Ang Mo Kio Street 23</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1520000</v>
+        <v>1350000</v>
       </c>
       <c r="E181" t="n">
-        <v>1238.79</v>
+        <v>1110.2</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -15157,61 +15159,57 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>1 Aug 2026</t>
+          <t>6 Aug 2026</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>Toa Payoh MRT</t>
-        </is>
-      </c>
+          <t>94 years (TOP 2021)</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" t="b">
         <v>1</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138b-lorong-1a-toa-payoh-500192670</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-228b-ang-mo-kio-street-23-500225300</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>***EXCLUSIVE LISTING***&lt;br /&gt;&lt;br /&gt;- Prime 1227 sqft home at Lorong 1A Toa Payoh.&lt;br /&gt;- within 10 mins walk to Toa Payoh Mrt, Braddell Mrt and Caldecott Mrt&lt;br /&gt;- Proximity to top schools: 1km from CHIJ PRIMARY (TOA PAYOH), Marymount Convent School and Kheng Cheng School&lt;br /&gt;- balcony in living r</t>
+          <t>Exclusive Listing&lt;br /&gt;&lt;br /&gt;UNIT HIGHLIGHTS&lt;br /&gt;- North-South facing&lt;br /&gt;- High floor&lt;br /&gt;- Unblocked city view&lt;br /&gt;- Standalone corner unit&lt;br /&gt;- Move-in condition&lt;br /&gt;&lt;br /&gt;LOCATION &amp; AMENITIES&lt;br /&gt;- Supermarket &amp; Eateries - right across &lt;br /&gt;- Mayflower MRT - ~5mins walk&lt;br /&gt;&lt;br /&gt;*3-mo</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>500198898</t>
+          <t>500210793</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15221,18 +15219,18 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>138A Lorong 1A Toa Payoh</t>
+          <t>228A Ang Mo Kio Street 23</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1550000</v>
+        <v>1388000</v>
       </c>
       <c r="E182" t="n">
-        <v>1231.14</v>
+        <v>1141.45</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -15247,59 +15245,51 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>15 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>Caldecott MRT</t>
-        </is>
-      </c>
+          <t>93 years (TOP 2020)</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500198898</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-228a-ang-mo-kio-street-23-500210793</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>UNIT FEATURES&lt;br /&gt;◇ Floor Area 117sqm = 1259sqft&lt;br /&gt;◇ Super High Floor &lt;br /&gt;◇ Unblocked View &lt;br /&gt;◇ 5rm DBSS With Balcony in Living Room and Master Bedroom&lt;br /&gt;◇ Bright and Breezy&lt;br /&gt;◇ No Direct West Sun &lt;br /&gt;◇ Within 10 Mins Walk to 3 Different MRT Stations and Lines!&lt;br /&gt;&lt;br /&gt;AMENITIES&lt;</t>
+          <t xml:space="preserve">*GENIUNE LISTING* by Element Properties&lt;br /&gt;By Appointment only. Call to book your viewing!&lt;br /&gt;&lt;br /&gt;Lease left: Approx. 94 years&lt;br /&gt;Corner Unit, North-South Facing, Stand Alone unit, Excellent Privacy&lt;br /&gt;New Listing • Renovated • Move-in Condition • Unblocked Views &lt;br /&gt;&lt;br /&gt;Property Flat </t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>500090293</t>
+          <t>25492867</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15309,18 +15299,18 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>105A Bidadari Park Drive</t>
+          <t>138C Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1550000</v>
+        <v>1400000</v>
       </c>
       <c r="E183" t="n">
-        <v>1274.67</v>
+        <v>1111.99</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -15335,7 +15325,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -15350,20 +15340,24 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>7 Aug 2026</t>
+          <t>19 Aug 2026</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>93 years (TOP 2020)</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr"/>
+          <t>85 years (TOP 2012)</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Braddell MRT</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="b">
         <v>0</v>
@@ -15371,19 +15365,19 @@
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-105a-bidadari-park-drive-500090293</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138c-lorong-1a-toa-payoh-25492867</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Available for Indian &amp; Others. Chinese quota filled for April'26&lt;br /&gt;Discover your dream home! &lt;br /&gt;This stunning 3 bedroom, 2 bathroom HDB unit for sale is now available at 105A, Bidadari Park Drive, Singapore. &lt;br /&gt;Spanning a generous 1216 sqft, this beautifully renovated space offers a modern </t>
+          <t xml:space="preserve">Spacious 5-Room HDB for Sale at 138C Lorong 1A Toa Payoh  &lt;br /&gt;(Not Eligible for Chinese Buyers Due to Ethnic Quota)&lt;br /&gt;&lt;br /&gt;Discover this well-maintained 5-room HDB flat located in the highly sought-after Toa Payoh area. Situated at 138C Lorong 1A Toa Payoh, this unit offers a perfect blend of </t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>500231634</t>
+          <t>60139647</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15393,18 +15387,18 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>109B Bidadari Park Drive</t>
+          <t>141 Lorong 2 Toa Payoh</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1580000</v>
+        <v>1448888</v>
       </c>
       <c r="E184" t="n">
-        <v>1299.34</v>
+        <v>1160.97</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -15419,7 +15413,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -15427,27 +15421,27 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>94 years (TOP 2021)</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr"/>
+          <t>72 years (TOP 1999)</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Toa Payoh MRT</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="b">
         <v>0</v>
@@ -15455,19 +15449,19 @@
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-109b-bidadari-park-drive-500231634</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-141-lorong-2-toa-payoh-60139647</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>NEW LISTINGany ethnic group is welcome - August 2026*&lt;br /&gt;&lt;br /&gt;TOP 5 REASONS WHY YOU WILL LOVE THIS UNIT AND LOCATION:&lt;br /&gt;1. Bright, High floor, Spacious, MBS view&lt;br /&gt;2. Spacious layout (Approx. 1216 SQFT)&lt;br /&gt;3. Modern Contemporary design&lt;br /&gt;4. Convenient access to public transports&lt;br /&gt;5</t>
+          <t>A once-in-a-lifetime chance to own the only 5-bedroom HDB unit currently available next to Toa Payoh MRT. With zero supply in the market, this is an extremely rare opportunity for families and investors.&lt;br /&gt;&lt;br /&gt;Premium High-Floor Living&lt;br /&gt;Bright and airy with floor-to-ceiling windows, offerin</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>500233729</t>
+          <t>500192670</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15477,18 +15471,18 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>109B Bidadari Park Drive</t>
+          <t>138B Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1580000</v>
+        <v>1520000</v>
       </c>
       <c r="E185" t="n">
-        <v>1299.34</v>
+        <v>1238.79</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -15503,7 +15497,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5PA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -15518,44 +15512,46 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>1 Aug 2026</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>94 years (TOP 2021)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Potong Pasir MRT</t>
+          <t>Toa Payoh MRT</t>
         </is>
       </c>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="b">
         <v>0</v>
       </c>
-      <c r="R185" t="inlineStr"/>
+      <c r="R185" t="b">
+        <v>1</v>
+      </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-109b-bidadari-park-drive-500233729</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138b-lorong-1a-toa-payoh-500192670</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>Exclusive listing. Rare opportunity to own a spacious 5-room home in the highly sought-after Bidadari estate!&lt;br /&gt;&lt;br /&gt;1,216 sqft / 113 sqm&lt;br /&gt;5-Room Improved&lt;br /&gt;3 Bed, 2 Bath&lt;br /&gt;Newly MOP unit&lt;br /&gt;&lt;br /&gt;✓ Spacious 1,216 sqft / 113 sqm layout&lt;br /&gt;✓ 5-Room Improved&lt;br /&gt;✓ 3 Bedrooms, 2 Bath</t>
+          <t>***EXCLUSIVE LISTING***&lt;br /&gt;&lt;br /&gt;- Prime 1227 sqft home at Lorong 1A Toa Payoh.&lt;br /&gt;- within 10 mins walk to Toa Payoh Mrt, Braddell Mrt and Caldecott Mrt&lt;br /&gt;- Proximity to top schools: 1km from CHIJ PRIMARY (TOA PAYOH), Marymount Convent School and Kheng Cheng School&lt;br /&gt;- balcony in living r</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>500107709</t>
+          <t>500198898</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15565,18 +15561,18 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>105A Bidadari Park Drive</t>
+          <t>138A Lorong 1A Toa Payoh</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1600000</v>
+        <v>1550000</v>
       </c>
       <c r="E186" t="n">
-        <v>1315.79</v>
+        <v>1231.14</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -15591,7 +15587,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>5PA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -15606,46 +15602,44 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>8 Aug 2026</t>
+          <t>15 Aug 2026</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>93 years (TOP 2020)</t>
+          <t>85 years (TOP 2012)</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Nearby MRT</t>
+          <t>Caldecott MRT</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="b">
-        <v>1</v>
-      </c>
-      <c r="R186" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-105a-bidadari-park-drive-500107709</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138a-lorong-1a-toa-payoh-500198898</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>Rare corner unit, minimal built-in&lt;br /&gt;High floor above 10th, unblocked view at 105A Bidadari &lt;br /&gt;No extension needed&lt;br /&gt;Main door faces straight south, living room window faces straight north&lt;br /&gt;Mins walk to nearby MRT Potong Pasir with covered walkway and lift to overhead bridge&lt;br /&gt;Covere</t>
+          <t>UNIT FEATURES&lt;br /&gt;◇ Floor Area 117sqm = 1259sqft&lt;br /&gt;◇ Super High Floor &lt;br /&gt;◇ Unblocked View &lt;br /&gt;◇ 5rm DBSS With Balcony in Living Room and Master Bedroom&lt;br /&gt;◇ Bright and Breezy&lt;br /&gt;◇ No Direct West Sun &lt;br /&gt;◇ Within 10 Mins Walk to 3 Different MRT Stations and Lines!&lt;br /&gt;&lt;br /&gt;AMENITIES&lt;</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>500191969</t>
+          <t>500090293</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15655,18 +15649,18 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>138B Lorong 1A Toa Payoh</t>
+          <t>105A Bidadari Park Drive</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1600000</v>
+        <v>1550000</v>
       </c>
       <c r="E187" t="n">
-        <v>1303.99</v>
+        <v>1274.67</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -15681,7 +15675,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>5PA</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -15696,17 +15690,17 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>7 Aug 2026</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>93 years (TOP 2020)</t>
         </is>
       </c>
       <c r="O187" t="inlineStr"/>
@@ -15717,19 +15711,19 @@
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138b-lorong-1a-toa-payoh-500191969</t>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-105a-bidadari-park-drive-500090293</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>Discover the ideal family sanctuary in this exceptional 5-room premium apartment located at Lorong 1A Toa Payoh. Situated on a high floor, this residence offers unblocked views and a bright, airy atmosphere. This property represents an outstanding investment opportunity in one of Singapore's most so</t>
+          <t xml:space="preserve">Available for Indian &amp; Others. Chinese quota filled for April'26&lt;br /&gt;Discover your dream home! &lt;br /&gt;This stunning 3 bedroom, 2 bathroom HDB unit for sale is now available at 105A, Bidadari Park Drive, Singapore. &lt;br /&gt;Spanning a generous 1216 sqft, this beautifully renovated space offers a modern </t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>500096085</t>
+          <t>500231634</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15739,18 +15733,18 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>139B Lorong 1A Toa Payoh</t>
+          <t>109B Bidadari Park Drive</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1620000</v>
+        <v>1580000</v>
       </c>
       <c r="E188" t="n">
-        <v>1286.74</v>
+        <v>1299.34</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -15765,7 +15759,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>5A</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -15780,17 +15774,17 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>19 Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>85 years (TOP 2012)</t>
+          <t>94 years (TOP 2021)</t>
         </is>
       </c>
       <c r="O188" t="inlineStr"/>
@@ -15798,15 +15792,361 @@
       <c r="Q188" t="b">
         <v>0</v>
       </c>
-      <c r="R188" t="b">
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-109b-bidadari-park-drive-500231634</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>NEW LISTINGany ethnic group is welcome - August 2026*&lt;br /&gt;&lt;br /&gt;TOP 5 REASONS WHY YOU WILL LOVE THIS UNIT AND LOCATION:&lt;br /&gt;1. Bright, High floor, Spacious, MBS view&lt;br /&gt;2. Spacious layout (Approx. 1216 SQFT)&lt;br /&gt;3. Modern Contemporary design&lt;br /&gt;4. Convenient access to public transports&lt;br /&gt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>500233729</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>hdb</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>109B Bidadari Park Drive</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1299.34</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>5I</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Middle</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>94 years (TOP 2021)</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Potong Pasir MRT</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="b">
+        <v>0</v>
+      </c>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-109b-bidadari-park-drive-500233729</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Exclusive listing. Rare opportunity to own a spacious 5-room home in the highly sought-after Bidadari estate!&lt;br /&gt;&lt;br /&gt;1,216 sqft / 113 sqm&lt;br /&gt;5-Room Improved&lt;br /&gt;3 Bed, 2 Bath&lt;br /&gt;Newly MOP unit&lt;br /&gt;&lt;br /&gt;✓ Spacious 1,216 sqft / 113 sqm layout&lt;br /&gt;✓ 5-Room Improved&lt;br /&gt;✓ 3 Bedrooms, 2 Bath</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>500107709</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>hdb</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>105A Bidadari Park Drive</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1315.79</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>5I</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>8 Aug 2026</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>93 years (TOP 2020)</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Nearby MRT</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="b">
         <v>1</v>
       </c>
-      <c r="S188" t="inlineStr">
+      <c r="R190" t="b">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-105a-bidadari-park-drive-500107709</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Rare corner unit, minimal built-in&lt;br /&gt;High floor above 10th, unblocked view at 105A Bidadari &lt;br /&gt;No extension needed&lt;br /&gt;Main door faces straight south, living room window faces straight north&lt;br /&gt;Mins walk to nearby MRT Potong Pasir with covered walkway and lift to overhead bridge&lt;br /&gt;Covere</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>500191969</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>hdb</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>138B Lorong 1A Toa Payoh</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1303.99</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>5PA</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>85 years (TOP 2012)</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="b">
+        <v>0</v>
+      </c>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-138b-lorong-1a-toa-payoh-500191969</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Discover the ideal family sanctuary in this exceptional 5-room premium apartment located at Lorong 1A Toa Payoh. Situated on a high floor, this residence offers unblocked views and a bright, airy atmosphere. This property represents an outstanding investment opportunity in one of Singapore's most so</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>500096085</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>hdb</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>139B Lorong 1A Toa Payoh</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1620000</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1286.74</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>85 years (TOP 2012)</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="b">
+        <v>0</v>
+      </c>
+      <c r="R192" t="b">
+        <v>1</v>
+      </c>
+      <c r="S192" t="inlineStr">
         <is>
           <t>https://www.propertyguru.com.sg/listing/hdb-for-sale-139b-lorong-1a-toa-payoh-500096085</t>
         </is>
       </c>
-      <c r="T188" t="inlineStr">
+      <c r="T192" t="inlineStr">
         <is>
           <t>Looking for a unit that is in central Toa Payoh? This unit is a must-see!&lt;br /&gt;&lt;br /&gt;Features of this unit:&lt;br /&gt;• Vacant unit, available immediately for sale&lt;br /&gt;• Prefer extension but can nego&lt;br /&gt;• This is a 5-room DBSS unit, Super-High Floor&lt;br /&gt;• Spacious Living Room, enjoy an open Dining ar</t>
         </is>
